--- a/docs/deliverables/out/Programme/Quality/BIBS_Coverage_BRD-02_FRS_Coverage_in_BIBS_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/Quality/BIBS_Coverage_BRD-02_FRS_Coverage_in_BIBS_v1.0.xlsx
@@ -1529,37 +1529,37 @@
         <v>275</v>
       </c>
       <c r="C5" s="12" t="n">
-        <v>90</v>
+        <v>275</v>
       </c>
       <c r="D5" s="12" t="n">
-        <v>133</v>
+        <v>0</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>52</v>
+        <v>0</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>32.7</v>
+        <v>100</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>81.09999999999999</v>
+        <v>100</v>
       </c>
       <c r="H5" s="12" t="n">
         <v>167</v>
       </c>
       <c r="I5" s="12" t="n">
-        <v>64</v>
+        <v>167</v>
       </c>
       <c r="J5" s="12" t="n">
-        <v>81</v>
+        <v>0</v>
       </c>
       <c r="K5" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>38.3</v>
+        <v>100</v>
       </c>
       <c r="M5" s="12" t="n">
-        <v>86.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -1572,37 +1572,37 @@
         <v>1</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E6" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H6" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="K6" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M6" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="7">
@@ -1658,16 +1658,16 @@
         <v>5</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="G8" s="12" t="n">
         <v>100</v>
@@ -1676,16 +1676,16 @@
         <v>7</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J8" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>28.6</v>
+        <v>100</v>
       </c>
       <c r="M8" s="12" t="n">
         <v>100</v>
@@ -1701,37 +1701,37 @@
         <v>22</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E9" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>9.1</v>
+        <v>100</v>
       </c>
       <c r="G9" s="12" t="n">
-        <v>54.5</v>
+        <v>100</v>
       </c>
       <c r="H9" s="12" t="n">
         <v>20</v>
       </c>
       <c r="I9" s="12" t="n">
-        <v>4</v>
+        <v>20</v>
       </c>
       <c r="J9" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K9" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="M9" s="12" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
     </row>
     <row r="10">
@@ -1744,37 +1744,37 @@
         <v>36</v>
       </c>
       <c r="C10" s="12" t="n">
-        <v>2</v>
+        <v>36</v>
       </c>
       <c r="D10" s="12" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="E10" s="12" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>5.6</v>
+        <v>100</v>
       </c>
       <c r="G10" s="12" t="n">
-        <v>38.9</v>
+        <v>100</v>
       </c>
       <c r="H10" s="12" t="n">
         <v>12</v>
       </c>
       <c r="I10" s="12" t="n">
-        <v>3</v>
+        <v>12</v>
       </c>
       <c r="J10" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K10" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="M10" s="12" t="n">
-        <v>91.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="11">
@@ -1787,16 +1787,16 @@
         <v>6</v>
       </c>
       <c r="C11" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="D11" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>100</v>
@@ -1805,16 +1805,16 @@
         <v>7</v>
       </c>
       <c r="I11" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="J11" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>14.3</v>
+        <v>100</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>100</v>
@@ -1830,37 +1830,37 @@
         <v>21</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>1</v>
+        <v>21</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="E12" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>4.8</v>
+        <v>100</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="H12" s="12" t="n">
         <v>7</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>28.6</v>
+        <v>100</v>
       </c>
       <c r="M12" s="12" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
     </row>
     <row r="13">
@@ -1873,37 +1873,37 @@
         <v>33</v>
       </c>
       <c r="C13" s="12" t="n">
-        <v>16</v>
+        <v>33</v>
       </c>
       <c r="D13" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E13" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>48.5</v>
+        <v>100</v>
       </c>
       <c r="G13" s="12" t="n">
-        <v>72.7</v>
+        <v>100</v>
       </c>
       <c r="H13" s="12" t="n">
         <v>18</v>
       </c>
       <c r="I13" s="12" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="J13" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K13" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M13" s="12" t="n">
-        <v>77.8</v>
+        <v>100</v>
       </c>
     </row>
     <row r="14">
@@ -1916,37 +1916,37 @@
         <v>4</v>
       </c>
       <c r="C14" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D14" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="E14" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
       <c r="H14" s="12" t="n">
         <v>4</v>
       </c>
       <c r="I14" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J14" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="J14" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="K14" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M14" s="12" t="n">
-        <v>75</v>
+        <v>100</v>
       </c>
     </row>
     <row r="15">
@@ -1959,16 +1959,16 @@
         <v>33</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="D15" s="12" t="n">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="E15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>39.4</v>
+        <v>100</v>
       </c>
       <c r="G15" s="12" t="n">
         <v>100</v>
@@ -1977,16 +1977,16 @@
         <v>11</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="J15" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>27.3</v>
+        <v>100</v>
       </c>
       <c r="M15" s="12" t="n">
         <v>100</v>
@@ -2002,37 +2002,37 @@
         <v>32</v>
       </c>
       <c r="C16" s="12" t="n">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="D16" s="12" t="n">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="E16" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>96.90000000000001</v>
+        <v>100</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>10</v>
       </c>
       <c r="I16" s="12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="J16" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K16" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -2045,37 +2045,37 @@
         <v>13</v>
       </c>
       <c r="C17" s="12" t="n">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="D17" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="E17" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>23.1</v>
+        <v>100</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>84.59999999999999</v>
+        <v>100</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>14</v>
       </c>
       <c r="I17" s="12" t="n">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="J17" s="12" t="n">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="K17" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>7.1</v>
+        <v>100</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>85.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18">
@@ -2088,16 +2088,16 @@
         <v>8</v>
       </c>
       <c r="C18" s="12" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="E18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>100</v>
@@ -2106,16 +2106,16 @@
         <v>4</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>100</v>
@@ -2131,16 +2131,16 @@
         <v>3</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>100</v>
@@ -2149,16 +2149,16 @@
         <v>6</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>100</v>
@@ -2174,37 +2174,37 @@
         <v>5</v>
       </c>
       <c r="C20" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E20" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="G20" s="12" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H20" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K20" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="M20" s="12" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="21">
@@ -2217,16 +2217,16 @@
         <v>4</v>
       </c>
       <c r="C21" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D21" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="D21" s="12" t="n">
-        <v>4</v>
       </c>
       <c r="E21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>100</v>
@@ -2235,16 +2235,16 @@
         <v>4</v>
       </c>
       <c r="I21" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J21" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="J21" s="12" t="n">
-        <v>4</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>100</v>
@@ -2260,16 +2260,16 @@
         <v>5</v>
       </c>
       <c r="C22" s="12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D22" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>100</v>
@@ -2278,16 +2278,16 @@
         <v>5</v>
       </c>
       <c r="I22" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J22" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>100</v>
@@ -2303,34 +2303,34 @@
         <v>24</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>6</v>
+        <v>24</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="E23" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>25</v>
+        <v>100</v>
       </c>
       <c r="G23" s="12" t="n">
-        <v>95.8</v>
+        <v>100</v>
       </c>
       <c r="H23" s="12" t="n">
         <v>6</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>100</v>
@@ -2733,16 +2733,16 @@
         <v>2</v>
       </c>
       <c r="C33" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D33" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>100</v>
@@ -2751,16 +2751,16 @@
         <v>2</v>
       </c>
       <c r="I33" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="J33" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>100</v>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="F5" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G5" s="12" t="inlineStr">
@@ -2913,7 +2913,7 @@
       </c>
       <c r="H5" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours does not restrict the device; the BRD asks for the same performance on mobile and desktop.</t>
+          <t>Device access test: with the device restriction set on, only the company networks and the company-issued devices reach the sign-in; the setting is off for SIT. Walkthrough on the browser of a laptop and of a tablet with the same screens.</t>
         </is>
       </c>
     </row>
@@ -3071,7 +3071,7 @@
       </c>
       <c r="F9" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
@@ -3081,7 +3081,7 @@
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours shows live counts per queue (unapplied, dispositions and receipt actions for approval, pre-booked, PDCs) without amounts and without per-type rows; no “for posting” or “returned” tiles because issuance posts at once.</t>
+          <t>Cashiering dashboard test: count and amount per receipt type and status for issuance, cancellation, reinstatement, returned records, unapplied payments and payment files; each item opens its list; shown within 5 seconds.</t>
         </is>
       </c>
     </row>
@@ -3113,7 +3113,7 @@
       </c>
       <c r="F10" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
@@ -3123,7 +3123,7 @@
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>Live counts per queue are available; the amounts per receipt type and status are planned for (C1 decides the posting items).</t>
+          <t>Cashiering dashboard test: count and amount per receipt type and status for issuance, cancellation, reinstatement, returned records, unapplied payments and payment files; each item opens its list; shown within 5 seconds.</t>
         </is>
       </c>
     </row>
@@ -3155,7 +3155,7 @@
       </c>
       <c r="F11" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
@@ -3165,7 +3165,7 @@
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours: Receive Payment, Receipts, Unapplied Payments, Incoming Requests, Pre-booked Payments, Payment Uploads, PDC Warehouse, Batch Print, Commission ORs, Receipt Series, Cashiering Setup; no separate posting entries.</t>
+          <t>Cashiering dashboard test: count and amount per receipt type and status for issuance, cancellation, reinstatement, returned records, unapplied payments and payment files; each item opens its list; shown within 5 seconds.</t>
         </is>
       </c>
     </row>
@@ -3197,7 +3197,7 @@
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
@@ -3207,7 +3207,7 @@
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours lists receipts and unapplied payments with filters; BDOI's columns (creation record number, receipt type, account / invoice, client, insurer) are partly shown.</t>
+          <t>Cashiering dashboard test: count and amount per receipt type and status for issuance, cancellation, reinstatement, returned records, unapplied payments and payment files; each item opens its list; shown within 5 seconds.</t>
         </is>
       </c>
     </row>
@@ -3239,7 +3239,7 @@
       </c>
       <c r="F13" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
@@ -3249,7 +3249,7 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours has the AR class (channels and non-premium types), payor, references, amount, currency, mode, check no. and bank, payment date. Not in ours: entry type, bank account to post to, receipting branch choice (ours uses the user's branch), the 1B limit, remarks.</t>
+          <t>Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -3281,7 +3281,7 @@
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
@@ -3291,7 +3291,7 @@
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>Payor, references, currency, mode and matching are available; entry type, bank account and receipting branch are planned for.</t>
+          <t>Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -3323,7 +3323,7 @@
       </c>
       <c r="F15" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
@@ -3333,7 +3333,7 @@
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours previews each invoice by component with the amount applied, the 2% CWT withheld and the excess; the payment is applied oldest first, not split per account by the user.</t>
+          <t>Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -3365,7 +3365,7 @@
       </c>
       <c r="F16" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
@@ -3375,7 +3375,7 @@
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours previews each invoice by component with the amount applied, the 2% CWT withheld and the excess; the payment is applied oldest first, not split per account by the user.</t>
+          <t>Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -3407,7 +3407,7 @@
       </c>
       <c r="F17" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
@@ -3417,7 +3417,7 @@
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours previews each invoice by component with the amount applied, the 2% CWT withheld and the excess; the payment is applied oldest first, not split per account by the user.</t>
+          <t>Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -3449,7 +3449,7 @@
       </c>
       <c r="F18" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Remarks and bank account are mandatory in BDOI's; ours has neither field.</t>
+          <t>Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="F19" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
@@ -3501,7 +3501,7 @@
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>Heading item: see its sub-items.</t>
+          <t>Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -3533,7 +3533,7 @@
       </c>
       <c r="F20" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G20" s="12" t="inlineStr">
@@ -3543,7 +3543,7 @@
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>Mandatory fields and amount checks are available; the currency and check-date checks are planned for (C7).</t>
+          <t>Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -3575,7 +3575,7 @@
       </c>
       <c r="F21" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G21" s="12" t="inlineStr">
@@ -3585,7 +3585,7 @@
       </c>
       <c r="H21" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours receipts in the currency received and converts at the BOOK rate; no check against the booked currency. Ours has no check-date check at receipt; a 3 banking day holding period applies before the payment is remitted (RMTID.017).</t>
+          <t>Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -3617,7 +3617,7 @@
       </c>
       <c r="F22" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G22" s="12" t="inlineStr">
@@ -3627,7 +3627,7 @@
       </c>
       <c r="H22" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours receipts in the currency received and converts at the BOOK rate; no check against the booked currency. Ours has no check-date check at receipt; a 3 banking day holding period applies before the payment is remitted (RMTID.017). Ours issues the AR when the cashier saves (“Issue AR and Apply”); there is no created record, request number or posting step.</t>
+          <t>Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="F23" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G23" s="12" t="inlineStr">
@@ -3669,7 +3669,7 @@
       </c>
       <c r="H23" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours receipts in the currency received and converts at the BOOK rate; no check against the booked currency. Ours has no check-date check at receipt; a 3 banking day holding period applies before the payment is remitted (RMTID.017). Ours issues the AR when the cashier saves (“Issue AR and Apply”); there is no created record, request number or posting step.</t>
+          <t>Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="F24" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>The creation record numbers follow the posting step (C1, C3).</t>
+          <t>Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -3743,7 +3743,7 @@
       </c>
       <c r="F25" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
@@ -3753,7 +3753,7 @@
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>Posting step planned for after decision C1.</t>
+          <t>Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -3785,7 +3785,7 @@
       </c>
       <c r="F26" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G26" s="12" t="inlineStr">
@@ -3795,7 +3795,7 @@
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>Heading item: see its sub-items.</t>
+          <t>Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -3827,7 +3827,7 @@
       </c>
       <c r="F27" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
@@ -3837,7 +3837,7 @@
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>Heading item: see its sub-items.</t>
+          <t>Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -3869,7 +3869,7 @@
       </c>
       <c r="F28" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G28" s="12" t="inlineStr">
@@ -3879,7 +3879,7 @@
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: No draft receipt to edit in ours.</t>
+          <t>Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="F29" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: No draft receipt to edit in ours.</t>
+          <t>Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -3953,7 +3953,7 @@
       </c>
       <c r="F30" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G30" s="12" t="inlineStr">
@@ -3963,7 +3963,7 @@
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: No draft receipt to edit in ours.</t>
+          <t>Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -3995,7 +3995,7 @@
       </c>
       <c r="F31" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G31" s="12" t="inlineStr">
@@ -4005,7 +4005,7 @@
       </c>
       <c r="H31" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: No draft receipt to edit in ours.</t>
+          <t>Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -4047,7 +4047,7 @@
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours records the seven items of the IT audit standard (adds origin of the event and success or failure).</t>
+          <t>Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -4079,7 +4079,7 @@
       </c>
       <c r="F33" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G33" s="12" t="inlineStr">
@@ -4089,7 +4089,7 @@
       </c>
       <c r="H33" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours: OR type (service fee, profit share, commission, incentive, others), payor, currency, mode, gross, VAT, withholding tax, 2307 certificate ref.; no bank account and no entry type.</t>
+          <t>OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="F34" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G34" s="12" t="inlineStr">
@@ -4131,7 +4131,7 @@
       </c>
       <c r="H34" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours: OR type (service fee, profit share, commission, incentive, others), payor, currency, mode, gross, VAT, withholding tax, 2307 certificate ref.; no bank account and no entry type.</t>
+          <t>OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -4163,7 +4163,7 @@
       </c>
       <c r="F35" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G35" s="12" t="inlineStr">
@@ -4173,7 +4173,7 @@
       </c>
       <c r="H35" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours uploads the commission payment details (insurer, payee, certificate, payment ref., invoice, basic commission, VAT, WTAX, date) from the Excel template; failed rows stay staged with their reason. BDOI's field list is blank.</t>
+          <t>OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -4205,7 +4205,7 @@
       </c>
       <c r="F36" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G36" s="12" t="inlineStr">
@@ -4215,7 +4215,7 @@
       </c>
       <c r="H36" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours uploads the commission payment details (insurer, payee, certificate, payment ref., invoice, basic commission, VAT, WTAX, date) from the Excel template; failed rows stay staged with their reason. BDOI's field list is blank.</t>
+          <t>OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -4247,7 +4247,7 @@
       </c>
       <c r="F37" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G37" s="12" t="inlineStr">
@@ -4257,7 +4257,7 @@
       </c>
       <c r="H37" s="12" t="inlineStr">
         <is>
-          <t>Duplicate refusal and the validation of the commission payment details are available; the .csv pipe template and 50 MB limit are planned for.</t>
+          <t>OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -4289,7 +4289,7 @@
       </c>
       <c r="F38" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G38" s="12" t="inlineStr">
@@ -4299,7 +4299,7 @@
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours uploads the commission payment details (insurer, payee, certificate, payment ref., invoice, basic commission, VAT, WTAX, date) from the Excel template; failed rows stay staged with their reason. BDOI's field list is blank.</t>
+          <t>OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -4331,7 +4331,7 @@
       </c>
       <c r="F39" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G39" s="12" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="H39" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours uploads the commission payment details (insurer, payee, certificate, payment ref., invoice, basic commission, VAT, WTAX, date) from the Excel template; failed rows stay staged with their reason. BDOI's field list is blank.</t>
+          <t>OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -4373,7 +4373,7 @@
       </c>
       <c r="F40" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G40" s="12" t="inlineStr">
@@ -4383,7 +4383,7 @@
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours uploads the commission payment details (insurer, payee, certificate, payment ref., invoice, basic commission, VAT, WTAX, date) from the Excel template; failed rows stay staged with their reason. BDOI's field list is blank.</t>
+          <t>OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -4415,7 +4415,7 @@
       </c>
       <c r="F41" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G41" s="12" t="inlineStr">
@@ -4425,7 +4425,7 @@
       </c>
       <c r="H41" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours uploads the commission payment details (insurer, payee, certificate, payment ref., invoice, basic commission, VAT, WTAX, date) from the Excel template; failed rows stay staged with their reason. BDOI's field list is blank.</t>
+          <t>OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -4457,7 +4457,7 @@
       </c>
       <c r="F42" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G42" s="12" t="inlineStr">
@@ -4467,7 +4467,7 @@
       </c>
       <c r="H42" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours uploads the commission payment details (insurer, payee, certificate, payment ref., invoice, basic commission, VAT, WTAX, date) from the Excel template; failed rows stay staged with their reason. BDOI's field list is blank.</t>
+          <t>OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="F43" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G43" s="12" t="inlineStr">
@@ -4509,7 +4509,7 @@
       </c>
       <c r="H43" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours uploads the commission payment details (insurer, payee, certificate, payment ref., invoice, basic commission, VAT, WTAX, date) from the Excel template; failed rows stay staged with their reason. BDOI's field list is blank.</t>
+          <t>OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -4551,7 +4551,7 @@
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>The nine fields of the commission payment details template are read.</t>
+          <t>OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -4583,7 +4583,7 @@
       </c>
       <c r="F45" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G45" s="12" t="inlineStr">
@@ -4593,7 +4593,7 @@
       </c>
       <c r="H45" s="12" t="inlineStr">
         <is>
-          <t>Selection of the SOA or fee invoice is planned for.</t>
+          <t>Other income test: an incentive OR lists the Valid for Collection SOAs of the insurer with their outstanding amounts, a fee OR the fee invoices of the client; the outstanding amount falls once the OR is posted.</t>
         </is>
       </c>
     </row>
@@ -4625,7 +4625,7 @@
       </c>
       <c r="F46" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G46" s="12" t="inlineStr">
@@ -4635,7 +4635,7 @@
       </c>
       <c r="H46" s="12" t="inlineStr">
         <is>
-          <t>One OR per insurer and certificate is available; the exact amount match and whole-file rule follow decision C10.</t>
+          <t>OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -4667,7 +4667,7 @@
       </c>
       <c r="F47" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G47" s="12" t="inlineStr">
@@ -4677,7 +4677,7 @@
       </c>
       <c r="H47" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours does not require the paid commission to equal the outstanding amount and processes the valid lines.</t>
+          <t>OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="F48" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G48" s="12" t="inlineStr">
@@ -4719,7 +4719,7 @@
       </c>
       <c r="H48" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours does not require the paid commission to equal the outstanding amount and processes the valid lines.</t>
+          <t>OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -4751,7 +4751,7 @@
       </c>
       <c r="F49" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G49" s="12" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="H49" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours does not require the paid commission to equal the outstanding amount and processes the valid lines.</t>
+          <t>OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -4793,7 +4793,7 @@
       </c>
       <c r="F50" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G50" s="12" t="inlineStr">
@@ -4803,7 +4803,7 @@
       </c>
       <c r="H50" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours does not require the paid commission to equal the outstanding amount and processes the valid lines.</t>
+          <t>OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -4835,7 +4835,7 @@
       </c>
       <c r="F51" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G51" s="12" t="inlineStr">
@@ -4845,7 +4845,7 @@
       </c>
       <c r="H51" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours does not require the paid commission to equal the outstanding amount and processes the valid lines.</t>
+          <t>OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -4877,7 +4877,7 @@
       </c>
       <c r="F52" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G52" s="12" t="inlineStr">
@@ -4887,7 +4887,7 @@
       </c>
       <c r="H52" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours issues the OR at once from the Head Office series.</t>
+          <t>OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="F53" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G53" s="12" t="inlineStr">
@@ -4929,7 +4929,7 @@
       </c>
       <c r="H53" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours issues the OR at once from the Head Office series.</t>
+          <t>OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -4961,7 +4961,7 @@
       </c>
       <c r="F54" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G54" s="12" t="inlineStr">
@@ -4971,7 +4971,7 @@
       </c>
       <c r="H54" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours issues the OR at once from the Head Office series.</t>
+          <t>OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -5003,7 +5003,7 @@
       </c>
       <c r="F55" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G55" s="12" t="inlineStr">
@@ -5013,7 +5013,7 @@
       </c>
       <c r="H55" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours issues the OR at once from the Head Office series.</t>
+          <t>OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -5045,7 +5045,7 @@
       </c>
       <c r="F56" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G56" s="12" t="inlineStr">
@@ -5055,7 +5055,7 @@
       </c>
       <c r="H56" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours issues the OR at once from the Head Office series.</t>
+          <t>OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -5087,7 +5087,7 @@
       </c>
       <c r="F57" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G57" s="12" t="inlineStr">
@@ -5097,7 +5097,7 @@
       </c>
       <c r="H57" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours issues the OR at once from the Head Office series.</t>
+          <t>OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -5129,7 +5129,7 @@
       </c>
       <c r="F58" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G58" s="12" t="inlineStr">
@@ -5139,7 +5139,7 @@
       </c>
       <c r="H58" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours issues the OR at once from the Head Office series.</t>
+          <t>OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -5171,7 +5171,7 @@
       </c>
       <c r="F59" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G59" s="12" t="inlineStr">
@@ -5181,7 +5181,7 @@
       </c>
       <c r="H59" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours issues the OR at once from the Head Office series.</t>
+          <t>OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -5213,7 +5213,7 @@
       </c>
       <c r="F60" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G60" s="12" t="inlineStr">
@@ -5223,7 +5223,7 @@
       </c>
       <c r="H60" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours issues the OR at once from the Head Office series.</t>
+          <t>OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="F61" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G61" s="12" t="inlineStr">
@@ -5265,7 +5265,7 @@
       </c>
       <c r="H61" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours issues the OR at once from the Head Office series.</t>
+          <t>OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="F62" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G62" s="12" t="inlineStr">
@@ -5307,7 +5307,7 @@
       </c>
       <c r="H62" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours issues the OR at once from the Head Office series.</t>
+          <t>OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -5339,7 +5339,7 @@
       </c>
       <c r="F63" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G63" s="12" t="inlineStr">
@@ -5349,7 +5349,7 @@
       </c>
       <c r="H63" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours issues the OR at once from the Head Office series.</t>
+          <t>OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -5381,7 +5381,7 @@
       </c>
       <c r="F64" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G64" s="12" t="inlineStr">
@@ -5391,7 +5391,7 @@
       </c>
       <c r="H64" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours issues the OR at once from the Head Office series.</t>
+          <t>OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -5423,7 +5423,7 @@
       </c>
       <c r="F65" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G65" s="12" t="inlineStr">
@@ -5433,7 +5433,7 @@
       </c>
       <c r="H65" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours issues the OR at once from the Head Office series.</t>
+          <t>OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -5465,7 +5465,7 @@
       </c>
       <c r="F66" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G66" s="12" t="inlineStr">
@@ -5475,7 +5475,7 @@
       </c>
       <c r="H66" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours issues the OR at once from the Head Office series.</t>
+          <t>OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -5507,7 +5507,7 @@
       </c>
       <c r="F67" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G67" s="12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="H67" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours issues the OR at once from the Head Office series.</t>
+          <t>OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -5549,7 +5549,7 @@
       </c>
       <c r="F68" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G68" s="12" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="H68" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours keeps a series per kind and branch with prefix, range, BIR ATP no. and warning level, authorised by a second user; no year field (the prefix can carry it).</t>
+          <t>Receipt series tests: series per receipting branch with its year and number format (prefix, year, branch indicator, sequence), authorised by another user, warning alert of the numbers left, OR series for Head Office only, end below the last number refused.</t>
         </is>
       </c>
     </row>
@@ -5591,7 +5591,7 @@
       </c>
       <c r="F69" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G69" s="12" t="inlineStr">
@@ -5601,7 +5601,7 @@
       </c>
       <c r="H69" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours keeps a series per kind and branch with prefix, range, BIR ATP no. and warning level, authorised by a second user; no year field (the prefix can carry it).</t>
+          <t>Receipt series tests: series per receipting branch with its year and number format (prefix, year, branch indicator, sequence), authorised by another user, warning alert of the numbers left, OR series for Head Office only, end below the last number refused.</t>
         </is>
       </c>
     </row>
@@ -5633,7 +5633,7 @@
       </c>
       <c r="F70" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G70" s="12" t="inlineStr">
@@ -5643,7 +5643,7 @@
       </c>
       <c r="H70" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours keeps a series per kind and branch with prefix, range, BIR ATP no. and warning level, authorised by a second user; no year field (the prefix can carry it).</t>
+          <t>Receipt series tests: series per receipting branch with its year and number format (prefix, year, branch indicator, sequence), authorised by another user, warning alert of the numbers left, OR series for Head Office only, end below the last number refused.</t>
         </is>
       </c>
     </row>
@@ -5675,7 +5675,7 @@
       </c>
       <c r="F71" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G71" s="12" t="inlineStr">
@@ -5685,7 +5685,7 @@
       </c>
       <c r="H71" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours keeps a series per kind and branch with prefix, range, BIR ATP no. and warning level, authorised by a second user; no year field (the prefix can carry it).</t>
+          <t>Receipt series tests: series per receipting branch with its year and number format (prefix, year, branch indicator, sequence), authorised by another user, warning alert of the numbers left, OR series for Head Office only, end below the last number refused.</t>
         </is>
       </c>
     </row>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="H72" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours audits before and after values and the authorisation.</t>
+          <t>Receipt series tests: series per receipting branch with its year and number format (prefix, year, branch indicator, sequence), authorised by another user, warning alert of the numbers left, OR series for Head Office only, end below the last number refused.</t>
         </is>
       </c>
     </row>
@@ -5759,7 +5759,7 @@
       </c>
       <c r="F73" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G73" s="12" t="inlineStr">
@@ -5769,7 +5769,7 @@
       </c>
       <c r="H73" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours filters by kind, insurer and dates, up to 500 receipts per batch; the FR names the BDOI location but the screen has no branch filter; no separate re-print search.</t>
+          <t>Receipt printing tests: print by branch or insurer and issue dates, print queue of the receipts the system generated, re-print by part of the number with the REPRINT mark and the print count, certificate number at the first print, Client's and company copies with the company copy kept on the receipt, ZIP of one PDF per receipt, at most 500 per batch, retry and skip in the print log. Walkthrough of the print preview.</t>
         </is>
       </c>
     </row>
@@ -5801,7 +5801,7 @@
       </c>
       <c r="F74" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G74" s="12" t="inlineStr">
@@ -5811,7 +5811,7 @@
       </c>
       <c r="H74" s="12" t="inlineStr">
         <is>
-          <t>Selection by filter is available; the print queue of system receipts is planned for.</t>
+          <t>Receipt printing tests: print by branch or insurer and issue dates, print queue of the receipts the system generated, re-print by part of the number with the REPRINT mark and the print count, certificate number at the first print, Client's and company copies with the company copy kept on the receipt, ZIP of one PDF per receipt, at most 500 per batch, retry and skip in the print log. Walkthrough of the print preview.</t>
         </is>
       </c>
     </row>
@@ -5843,7 +5843,7 @@
       </c>
       <c r="F75" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G75" s="12" t="inlineStr">
@@ -5853,7 +5853,7 @@
       </c>
       <c r="H75" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours filters by kind, insurer and dates, up to 500 receipts per batch; the FR names the BDOI location but the screen has no branch filter; no separate re-print search.</t>
+          <t>Receipt printing tests: print by branch or insurer and issue dates, print queue of the receipts the system generated, re-print by part of the number with the REPRINT mark and the print count, certificate number at the first print, Client's and company copies with the company copy kept on the receipt, ZIP of one PDF per receipt, at most 500 per batch, retry and skip in the print log. Walkthrough of the print preview.</t>
         </is>
       </c>
     </row>
@@ -5885,7 +5885,7 @@
       </c>
       <c r="F76" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G76" s="12" t="inlineStr">
@@ -5895,7 +5895,7 @@
       </c>
       <c r="H76" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours filters by kind, insurer and dates, up to 500 receipts per batch; the FR names the BDOI location but the screen has no branch filter; no separate re-print search.</t>
+          <t>Receipt printing tests: print by branch or insurer and issue dates, print queue of the receipts the system generated, re-print by part of the number with the REPRINT mark and the print count, certificate number at the first print, Client's and company copies with the company copy kept on the receipt, ZIP of one PDF per receipt, at most 500 per batch, retry and skip in the print log. Walkthrough of the print preview.</t>
         </is>
       </c>
     </row>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="F77" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G77" s="12" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="H77" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours filters by kind, insurer and dates, up to 500 receipts per batch; the FR names the BDOI location but the screen has no branch filter; no separate re-print search.</t>
+          <t>Receipt printing tests: print by branch or insurer and issue dates, print queue of the receipts the system generated, re-print by part of the number with the REPRINT mark and the print count, certificate number at the first print, Client's and company copies with the company copy kept on the receipt, ZIP of one PDF per receipt, at most 500 per batch, retry and skip in the print log. Walkthrough of the print preview.</t>
         </is>
       </c>
     </row>
@@ -5969,7 +5969,7 @@
       </c>
       <c r="F78" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G78" s="12" t="inlineStr">
@@ -5979,7 +5979,7 @@
       </c>
       <c r="H78" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours prints the AR / OR PDF (layout draft); no acknowledgement certificate number.</t>
+          <t>Receipt printing tests: print by branch or insurer and issue dates, print queue of the receipts the system generated, re-print by part of the number with the REPRINT mark and the print count, certificate number at the first print, Client's and company copies with the company copy kept on the receipt, ZIP of one PDF per receipt, at most 500 per batch, retry and skip in the print log. Walkthrough of the print preview.</t>
         </is>
       </c>
     </row>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="F79" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G79" s="12" t="inlineStr">
@@ -6021,7 +6021,7 @@
       </c>
       <c r="H79" s="12" t="inlineStr">
         <is>
-          <t>Certificate number planned for (C4).</t>
+          <t>Receipt printing tests: print by branch or insurer and issue dates, print queue of the receipts the system generated, re-print by part of the number with the REPRINT mark and the print count, certificate number at the first print, Client's and company copies with the company copy kept on the receipt, ZIP of one PDF per receipt, at most 500 per batch, retry and skip in the print log. Walkthrough of the print preview.</t>
         </is>
       </c>
     </row>
@@ -6053,7 +6053,7 @@
       </c>
       <c r="F80" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G80" s="12" t="inlineStr">
@@ -6063,7 +6063,7 @@
       </c>
       <c r="H80" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours produces one merged PDF per print batch.</t>
+          <t>Receipt printing tests: print by branch or insurer and issue dates, print queue of the receipts the system generated, re-print by part of the number with the REPRINT mark and the print count, certificate number at the first print, Client's and company copies with the company copy kept on the receipt, ZIP of one PDF per receipt, at most 500 per batch, retry and skip in the print log. Walkthrough of the print preview.</t>
         </is>
       </c>
     </row>
@@ -6095,7 +6095,7 @@
       </c>
       <c r="F81" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G81" s="12" t="inlineStr">
@@ -6105,7 +6105,7 @@
       </c>
       <c r="H81" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours produces one merged PDF per print batch.</t>
+          <t>Receipt printing tests: print by branch or insurer and issue dates, print queue of the receipts the system generated, re-print by part of the number with the REPRINT mark and the print count, certificate number at the first print, Client's and company copies with the company copy kept on the receipt, ZIP of one PDF per receipt, at most 500 per batch, retry and skip in the print log. Walkthrough of the print preview.</t>
         </is>
       </c>
     </row>
@@ -6137,7 +6137,7 @@
       </c>
       <c r="F82" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G82" s="12" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="H82" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours produces one merged PDF per print batch.</t>
+          <t>Receipt printing tests: print by branch or insurer and issue dates, print queue of the receipts the system generated, re-print by part of the number with the REPRINT mark and the print count, certificate number at the first print, Client's and company copies with the company copy kept on the receipt, ZIP of one PDF per receipt, at most 500 per batch, retry and skip in the print log. Walkthrough of the print preview.</t>
         </is>
       </c>
     </row>
@@ -6179,7 +6179,7 @@
       </c>
       <c r="F83" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G83" s="12" t="inlineStr">
@@ -6189,7 +6189,7 @@
       </c>
       <c r="H83" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours produces one merged PDF per print batch.</t>
+          <t>Receipt printing tests: print by branch or insurer and issue dates, print queue of the receipts the system generated, re-print by part of the number with the REPRINT mark and the print count, certificate number at the first print, Client's and company copies with the company copy kept on the receipt, ZIP of one PDF per receipt, at most 500 per batch, retry and skip in the print log. Walkthrough of the print preview.</t>
         </is>
       </c>
     </row>
@@ -6221,7 +6221,7 @@
       </c>
       <c r="F84" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G84" s="12" t="inlineStr">
@@ -6231,7 +6231,7 @@
       </c>
       <c r="H84" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours produces one merged PDF per print batch.</t>
+          <t>Receipt printing tests: print by branch or insurer and issue dates, print queue of the receipts the system generated, re-print by part of the number with the REPRINT mark and the print count, certificate number at the first print, Client's and company copies with the company copy kept on the receipt, ZIP of one PDF per receipt, at most 500 per batch, retry and skip in the print log. Walkthrough of the print preview.</t>
         </is>
       </c>
     </row>
@@ -6263,7 +6263,7 @@
       </c>
       <c r="F85" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G85" s="12" t="inlineStr">
@@ -6273,7 +6273,7 @@
       </c>
       <c r="H85" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours previews the list and prints the merged PDF from the browser.</t>
+          <t>Receipt printing tests: print by branch or insurer and issue dates, print queue of the receipts the system generated, re-print by part of the number with the REPRINT mark and the print count, certificate number at the first print, Client's and company copies with the company copy kept on the receipt, ZIP of one PDF per receipt, at most 500 per batch, retry and skip in the print log. Walkthrough of the print preview.</t>
         </is>
       </c>
     </row>
@@ -6305,7 +6305,7 @@
       </c>
       <c r="F86" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G86" s="12" t="inlineStr">
@@ -6315,7 +6315,7 @@
       </c>
       <c r="H86" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours previews the list and prints the merged PDF from the browser.</t>
+          <t>Receipt printing tests: print by branch or insurer and issue dates, print queue of the receipts the system generated, re-print by part of the number with the REPRINT mark and the print count, certificate number at the first print, Client's and company copies with the company copy kept on the receipt, ZIP of one PDF per receipt, at most 500 per batch, retry and skip in the print log. Walkthrough of the print preview.</t>
         </is>
       </c>
     </row>
@@ -6347,7 +6347,7 @@
       </c>
       <c r="F87" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G87" s="12" t="inlineStr">
@@ -6357,7 +6357,7 @@
       </c>
       <c r="H87" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours previews the list and prints the merged PDF from the browser.</t>
+          <t>Receipt printing tests: print by branch or insurer and issue dates, print queue of the receipts the system generated, re-print by part of the number with the REPRINT mark and the print count, certificate number at the first print, Client's and company copies with the company copy kept on the receipt, ZIP of one PDF per receipt, at most 500 per batch, retry and skip in the print log. Walkthrough of the print preview.</t>
         </is>
       </c>
     </row>
@@ -6389,7 +6389,7 @@
       </c>
       <c r="F88" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G88" s="12" t="inlineStr">
@@ -6399,7 +6399,7 @@
       </c>
       <c r="H88" s="12" t="inlineStr">
         <is>
-          <t>The print count is kept; the REPRINT mark is planned for.</t>
+          <t>Receipt printing tests: print by branch or insurer and issue dates, print queue of the receipts the system generated, re-print by part of the number with the REPRINT mark and the print count, certificate number at the first print, Client's and company copies with the company copy kept on the receipt, ZIP of one PDF per receipt, at most 500 per batch, retry and skip in the print log. Walkthrough of the print preview.</t>
         </is>
       </c>
     </row>
@@ -6431,7 +6431,7 @@
       </c>
       <c r="F89" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G89" s="12" t="inlineStr">
@@ -6441,7 +6441,7 @@
       </c>
       <c r="H89" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours lists failures and retries them; skip is implicit.</t>
+          <t>Receipt printing tests: print by branch or insurer and issue dates, print queue of the receipts the system generated, re-print by part of the number with the REPRINT mark and the print count, certificate number at the first print, Client's and company copies with the company copy kept on the receipt, ZIP of one PDF per receipt, at most 500 per batch, retry and skip in the print log. Walkthrough of the print preview.</t>
         </is>
       </c>
     </row>
@@ -6473,7 +6473,7 @@
       </c>
       <c r="F90" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G90" s="12" t="inlineStr">
@@ -6483,7 +6483,7 @@
       </c>
       <c r="H90" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours lists failures and retries them; skip is implicit.</t>
+          <t>Receipt printing tests: print by branch or insurer and issue dates, print queue of the receipts the system generated, re-print by part of the number with the REPRINT mark and the print count, certificate number at the first print, Client's and company copies with the company copy kept on the receipt, ZIP of one PDF per receipt, at most 500 per batch, retry and skip in the print log. Walkthrough of the print preview.</t>
         </is>
       </c>
     </row>
@@ -6515,7 +6515,7 @@
       </c>
       <c r="F91" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G91" s="12" t="inlineStr">
@@ -6525,7 +6525,7 @@
       </c>
       <c r="H91" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours lists failures and retries them; skip is implicit.</t>
+          <t>Receipt printing tests: print by branch or insurer and issue dates, print queue of the receipts the system generated, re-print by part of the number with the REPRINT mark and the print count, certificate number at the first print, Client's and company copies with the company copy kept on the receipt, ZIP of one PDF per receipt, at most 500 per batch, retry and skip in the print log. Walkthrough of the print preview.</t>
         </is>
       </c>
     </row>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="H92" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours logs user, time and count per batch and the print count per receipt.</t>
+          <t>Receipt printing tests: print by branch or insurer and issue dates, print queue of the receipts the system generated, re-print by part of the number with the REPRINT mark and the print count, certificate number at the first print, Client's and company copies with the company copy kept on the receipt, ZIP of one PDF per receipt, at most 500 per batch, retry and skip in the print log. Walkthrough of the print preview.</t>
         </is>
       </c>
     </row>
@@ -6599,7 +6599,7 @@
       </c>
       <c r="F93" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G93" s="12" t="inlineStr">
@@ -6609,7 +6609,7 @@
       </c>
       <c r="H93" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: No posting list or poster role for issuance in ours.</t>
+          <t>Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -6641,7 +6641,7 @@
       </c>
       <c r="F94" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G94" s="12" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="H94" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: No posting list or poster role for issuance in ours.</t>
+          <t>Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -6683,7 +6683,7 @@
       </c>
       <c r="F95" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G95" s="12" t="inlineStr">
@@ -6693,7 +6693,7 @@
       </c>
       <c r="H95" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: No posting list or poster role for issuance in ours.</t>
+          <t>Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -6725,7 +6725,7 @@
       </c>
       <c r="F96" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G96" s="12" t="inlineStr">
@@ -6735,7 +6735,7 @@
       </c>
       <c r="H96" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: No posting list or poster role for issuance in ours.</t>
+          <t>Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -6767,7 +6767,7 @@
       </c>
       <c r="F97" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G97" s="12" t="inlineStr">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="H97" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: No posting list or poster role for issuance in ours.</t>
+          <t>Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -6809,7 +6809,7 @@
       </c>
       <c r="F98" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G98" s="12" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="H98" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: No posting list or poster role for issuance in ours.</t>
+          <t>Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -6851,7 +6851,7 @@
       </c>
       <c r="F99" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G99" s="12" t="inlineStr">
@@ -6861,7 +6861,7 @@
       </c>
       <c r="H99" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: No posting list or poster role for issuance in ours.</t>
+          <t>Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -6893,7 +6893,7 @@
       </c>
       <c r="F100" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G100" s="12" t="inlineStr">
@@ -6903,7 +6903,7 @@
       </c>
       <c r="H100" s="12" t="inlineStr">
         <is>
-          <t>Posting step planned for after decision C1.</t>
+          <t>Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -6935,7 +6935,7 @@
       </c>
       <c r="F101" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G101" s="12" t="inlineStr">
@@ -6945,7 +6945,7 @@
       </c>
       <c r="H101" s="12" t="inlineStr">
         <is>
-          <t>Return of a creation record follows the posting step (C1).</t>
+          <t>Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -6977,7 +6977,7 @@
       </c>
       <c r="F102" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G102" s="12" t="inlineStr">
@@ -6987,7 +6987,7 @@
       </c>
       <c r="H102" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours guarantees no duplicates; a sequence without gaps is not stated.</t>
+          <t>Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -7019,7 +7019,7 @@
       </c>
       <c r="F103" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G103" s="12" t="inlineStr">
@@ -7029,7 +7029,7 @@
       </c>
       <c r="H103" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours guarantees no duplicates; a sequence without gaps is not stated.</t>
+          <t>Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -7061,7 +7061,7 @@
       </c>
       <c r="F104" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G104" s="12" t="inlineStr">
@@ -7071,7 +7071,7 @@
       </c>
       <c r="H104" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours guarantees no duplicates; a sequence without gaps is not stated.</t>
+          <t>Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -7103,7 +7103,7 @@
       </c>
       <c r="F105" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G105" s="12" t="inlineStr">
@@ -7113,7 +7113,7 @@
       </c>
       <c r="H105" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours guarantees no duplicates; a sequence without gaps is not stated.</t>
+          <t>Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -7155,7 +7155,7 @@
       </c>
       <c r="H106" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Same rule; ours shows “No authorized &lt;kind&gt; series with numbers left for this branch (CSHID.015)”.</t>
+          <t>Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -7197,7 +7197,7 @@
       </c>
       <c r="H107" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Same rule; ours shows “No authorized &lt;kind&gt; series with numbers left for this branch (CSHID.015)”.</t>
+          <t>Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -7239,7 +7239,7 @@
       </c>
       <c r="H108" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Same rule; ours shows “No authorized &lt;kind&gt; series with numbers left for this branch (CSHID.015)”.</t>
+          <t>Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -7281,7 +7281,7 @@
       </c>
       <c r="H109" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Same rule; ours shows “No authorized &lt;kind&gt; series with numbers left for this branch (CSHID.015)”.</t>
+          <t>Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -7323,7 +7323,7 @@
       </c>
       <c r="H110" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Same rule; ours shows “No authorized &lt;kind&gt; series with numbers left for this branch (CSHID.015)”.</t>
+          <t>Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -7365,7 +7365,7 @@
       </c>
       <c r="H111" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: -</t>
+          <t>Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -7407,7 +7407,7 @@
       </c>
       <c r="H112" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: -</t>
+          <t>Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -7449,7 +7449,7 @@
       </c>
       <c r="H113" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: -</t>
+          <t>Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -7481,7 +7481,7 @@
       </c>
       <c r="F114" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G114" s="12" t="inlineStr">
@@ -7491,7 +7491,7 @@
       </c>
       <c r="H114" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours inserts FST after LGT; check before cash is open. BDOI's review comment: “Confirm first with Insurers for payment hierarchy”.</t>
+          <t>Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -7523,7 +7523,7 @@
       </c>
       <c r="F115" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G115" s="12" t="inlineStr">
@@ -7533,7 +7533,7 @@
       </c>
       <c r="H115" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours inserts FST after LGT; check before cash is open. BDOI's review comment: “Confirm first with Insurers for payment hierarchy”.</t>
+          <t>Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -7575,7 +7575,7 @@
       </c>
       <c r="H116" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Same rule and exceptions; ours defaults to 10.00 (BRD Php 10.00) and moves a minimal excess to AP overages.</t>
+          <t>Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="H117" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Same rule and exceptions; ours defaults to 10.00 (BRD Php 10.00) and moves a minimal excess to AP overages.</t>
+          <t>Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -7659,7 +7659,7 @@
       </c>
       <c r="H118" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Same rule and exceptions; ours defaults to 10.00 (BRD Php 10.00) and moves a minimal excess to AP overages.</t>
+          <t>Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -7701,7 +7701,7 @@
       </c>
       <c r="H119" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Same rule and exceptions; ours defaults to 10.00 (BRD Php 10.00) and moves a minimal excess to AP overages.</t>
+          <t>Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -7743,7 +7743,7 @@
       </c>
       <c r="H120" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Same rule and exceptions; ours defaults to 10.00 (BRD Php 10.00) and moves a minimal excess to AP overages.</t>
+          <t>Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="F121" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G121" s="12" t="inlineStr">
@@ -7785,7 +7785,7 @@
       </c>
       <c r="H121" s="12" t="inlineStr">
         <is>
-          <t>The 98% application for 2% CWT clients is available; the tag per account follows decision C26.</t>
+          <t>Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -7817,7 +7817,7 @@
       </c>
       <c r="F122" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G122" s="12" t="inlineStr">
@@ -7827,7 +7827,7 @@
       </c>
       <c r="H122" s="12" t="inlineStr">
         <is>
-          <t>One OR per group is issued; the print queue is planned for.</t>
+          <t>Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -7869,7 +7869,7 @@
       </c>
       <c r="H123" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours posts at the Comptrollership BOOK rate (2 decimals) and gives the default entries.</t>
+          <t>Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -7911,7 +7911,7 @@
       </c>
       <c r="H124" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours posts at the Comptrollership BOOK rate (2 decimals) and gives the default entries.</t>
+          <t>Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -7943,7 +7943,7 @@
       </c>
       <c r="F125" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G125" s="12" t="inlineStr">
@@ -7953,7 +7953,7 @@
       </c>
       <c r="H125" s="12" t="inlineStr">
         <is>
-          <t>Template maintenance of the AR and OR forms planned for (C16).</t>
+          <t>Receipt form tests: AR and OR forms with the company address and VAT TIN, the amount in words and in figures, footer lines and copy label; a form change printed only after another user approved it. Certification of Payment test with its series number.</t>
         </is>
       </c>
     </row>
@@ -7985,7 +7985,7 @@
       </c>
       <c r="F126" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G126" s="12" t="inlineStr">
@@ -7995,7 +7995,7 @@
       </c>
       <c r="H126" s="12" t="inlineStr">
         <is>
-          <t>The OR PDF is available with the company name; BDOI's header, footer and words are planned for.</t>
+          <t>Receipt form tests: AR and OR forms with the company address and VAT TIN, the amount in words and in figures, footer lines and copy label; a form change printed only after another user approved it. Certification of Payment test with its series number.</t>
         </is>
       </c>
     </row>
@@ -8027,7 +8027,7 @@
       </c>
       <c r="F127" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G127" s="12" t="inlineStr">
@@ -8037,7 +8037,7 @@
       </c>
       <c r="H127" s="12" t="inlineStr">
         <is>
-          <t>The AR PDF is available; BDOI's form is planned for.</t>
+          <t>Receipt form tests: AR and OR forms with the company address and VAT TIN, the amount in words and in figures, footer lines and copy label; a form change printed only after another user approved it. Certification of Payment test with its series number.</t>
         </is>
       </c>
     </row>
@@ -8079,7 +8079,7 @@
       </c>
       <c r="H128" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours searches receipts and cancels from the receipt page.</t>
+          <t>Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -8121,7 +8121,7 @@
       </c>
       <c r="H129" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours searches receipts and cancels from the receipt page.</t>
+          <t>Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -8163,7 +8163,7 @@
       </c>
       <c r="H130" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours searches receipts and cancels from the receipt page.</t>
+          <t>Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -8205,7 +8205,7 @@
       </c>
       <c r="H131" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours searches receipts and cancels from the receipt page.</t>
+          <t>Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -8247,7 +8247,7 @@
       </c>
       <c r="H132" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours searches receipts and cancels from the receipt page.</t>
+          <t>Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -8289,7 +8289,7 @@
       </c>
       <c r="H133" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours searches receipts and cancels from the receipt page.</t>
+          <t>Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -8321,7 +8321,7 @@
       </c>
       <c r="F134" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G134" s="12" t="inlineStr">
@@ -8331,7 +8331,7 @@
       </c>
       <c r="H134" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours cancels one receipt per request. Ours has the BRD list in four groups (premium, commission, PDC, general); no restriction by payment type.</t>
+          <t>Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -8363,7 +8363,7 @@
       </c>
       <c r="F135" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G135" s="12" t="inlineStr">
@@ -8373,7 +8373,7 @@
       </c>
       <c r="H135" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours cancels one receipt per request. Ours has the BRD list in four groups (premium, commission, PDC, general); no restriction by payment type.</t>
+          <t>Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -8405,7 +8405,7 @@
       </c>
       <c r="F136" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G136" s="12" t="inlineStr">
@@ -8415,7 +8415,7 @@
       </c>
       <c r="H136" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours cancels one receipt per request. Ours has the BRD list in four groups (premium, commission, PDC, general); no restriction by payment type.</t>
+          <t>Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -8447,7 +8447,7 @@
       </c>
       <c r="F137" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G137" s="12" t="inlineStr">
@@ -8457,7 +8457,7 @@
       </c>
       <c r="H137" s="12" t="inlineStr">
         <is>
-          <t>Reason, waiting request and disposition checks are available; the check-payment restriction is planned for (C21).</t>
+          <t>Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -8489,7 +8489,7 @@
       </c>
       <c r="F138" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G138" s="12" t="inlineStr">
@@ -8499,7 +8499,7 @@
       </c>
       <c r="H138" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours has the BRD list in four groups (premium, commission, PDC, general); no restriction by payment type.</t>
+          <t>Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -8531,7 +8531,7 @@
       </c>
       <c r="F139" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G139" s="12" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="H139" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours has the BRD list in four groups (premium, commission, PDC, general); no restriction by payment type.</t>
+          <t>Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -8573,7 +8573,7 @@
       </c>
       <c r="F140" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G140" s="12" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="H140" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours has the BRD list in four groups (premium, commission, PDC, general); no restriction by payment type. Same maker-checker; ours numbers CAN-yyyy-n (BDOI CN-AR / CN-OR) and its stages are Requested, For approval, Posted.</t>
+          <t>Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -8615,7 +8615,7 @@
       </c>
       <c r="F141" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G141" s="12" t="inlineStr">
@@ -8625,7 +8625,7 @@
       </c>
       <c r="H141" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours has the BRD list in four groups (premium, commission, PDC, general); no restriction by payment type. Same maker-checker; ours numbers CAN-yyyy-n (BDOI CN-AR / CN-OR) and its stages are Requested, For approval, Posted.</t>
+          <t>Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -8657,7 +8657,7 @@
       </c>
       <c r="F142" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G142" s="12" t="inlineStr">
@@ -8667,7 +8667,7 @@
       </c>
       <c r="H142" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours has the BRD list in four groups (premium, commission, PDC, general); no restriction by payment type. Same maker-checker; ours numbers CAN-yyyy-n (BDOI CN-AR / CN-OR) and its stages are Requested, For approval, Posted.</t>
+          <t>Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -8699,7 +8699,7 @@
       </c>
       <c r="F143" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G143" s="12" t="inlineStr">
@@ -8709,7 +8709,7 @@
       </c>
       <c r="H143" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours has the BRD list in four groups (premium, commission, PDC, general); no restriction by payment type. Same maker-checker; ours numbers CAN-yyyy-n (BDOI CN-AR / CN-OR) and its stages are Requested, For approval, Posted.</t>
+          <t>Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -8741,7 +8741,7 @@
       </c>
       <c r="F144" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G144" s="12" t="inlineStr">
@@ -8751,7 +8751,7 @@
       </c>
       <c r="H144" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours has the BRD list in four groups (premium, commission, PDC, general); no restriction by payment type. Same maker-checker; ours numbers CAN-yyyy-n (BDOI CN-AR / CN-OR) and its stages are Requested, For approval, Posted.</t>
+          <t>Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -8793,7 +8793,7 @@
       </c>
       <c r="H145" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours lets the requester correct and resubmit a returned request or withdraw it.</t>
+          <t>Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -8835,7 +8835,7 @@
       </c>
       <c r="H146" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours lets the requester correct and resubmit a returned request or withdraw it.</t>
+          <t>Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -8877,7 +8877,7 @@
       </c>
       <c r="H147" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours lets the requester correct and resubmit a returned request or withdraw it.</t>
+          <t>Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -8909,7 +8909,7 @@
       </c>
       <c r="F148" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G148" s="12" t="inlineStr">
@@ -8919,7 +8919,7 @@
       </c>
       <c r="H148" s="12" t="inlineStr">
         <is>
-          <t>Reversal and four eyes are available; the remitted branch follows decision C9.</t>
+          <t>Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -8951,7 +8951,7 @@
       </c>
       <c r="F149" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G149" s="12" t="inlineStr">
@@ -8961,7 +8961,7 @@
       </c>
       <c r="H149" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours reverses every application so the invoices are outstanding again; there is no remitted / not remitted branch.</t>
+          <t>Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -8993,7 +8993,7 @@
       </c>
       <c r="F150" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G150" s="12" t="inlineStr">
@@ -9003,7 +9003,7 @@
       </c>
       <c r="H150" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours reverses every application so the invoices are outstanding again; there is no remitted / not remitted branch.</t>
+          <t>Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -9035,7 +9035,7 @@
       </c>
       <c r="F151" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G151" s="12" t="inlineStr">
@@ -9045,7 +9045,7 @@
       </c>
       <c r="H151" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours reverses every application so the invoices are outstanding again; there is no remitted / not remitted branch.</t>
+          <t>Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -9077,7 +9077,7 @@
       </c>
       <c r="F152" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G152" s="12" t="inlineStr">
@@ -9087,7 +9087,7 @@
       </c>
       <c r="H152" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours reverses every application so the invoices are outstanding again; there is no remitted / not remitted branch.</t>
+          <t>Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -9119,7 +9119,7 @@
       </c>
       <c r="F153" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G153" s="12" t="inlineStr">
@@ -9129,7 +9129,7 @@
       </c>
       <c r="H153" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours reverses every application so the invoices are outstanding again; there is no remitted / not remitted branch.</t>
+          <t>Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -9161,7 +9161,7 @@
       </c>
       <c r="F154" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G154" s="12" t="inlineStr">
@@ -9171,7 +9171,7 @@
       </c>
       <c r="H154" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours reverses every application so the invoices are outstanding again; there is no remitted / not remitted branch.</t>
+          <t>Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -9203,7 +9203,7 @@
       </c>
       <c r="F155" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G155" s="12" t="inlineStr">
@@ -9213,7 +9213,7 @@
       </c>
       <c r="H155" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours reverses every application so the invoices are outstanding again; there is no remitted / not remitted branch.</t>
+          <t>Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -9245,7 +9245,7 @@
       </c>
       <c r="F156" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G156" s="12" t="inlineStr">
@@ -9255,7 +9255,7 @@
       </c>
       <c r="H156" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours reverses every application so the invoices are outstanding again; there is no remitted / not remitted branch.</t>
+          <t>Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -9297,7 +9297,7 @@
       </c>
       <c r="H157" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours re-posts the original events negative at the original BOOK rate.</t>
+          <t>Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -9339,7 +9339,7 @@
       </c>
       <c r="H158" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours re-posts the original events negative at the original BOOK rate.</t>
+          <t>Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -9381,7 +9381,7 @@
       </c>
       <c r="H159" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: -</t>
+          <t>Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -9423,7 +9423,7 @@
       </c>
       <c r="H160" s="12" t="inlineStr">
         <is>
-          <t>Shown working in the end-to-end run; criteria without an automated check are confirmed in UAT.</t>
+          <t>Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -9455,7 +9455,7 @@
       </c>
       <c r="F161" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G161" s="12" t="inlineStr">
@@ -9465,7 +9465,7 @@
       </c>
       <c r="H161" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours reinstates a cancelled receipt; reversing the application of an issued receipt is the payment reversal requested by Accounting Controls and approved by the Cashiering TL.</t>
+          <t>Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -9497,7 +9497,7 @@
       </c>
       <c r="F162" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G162" s="12" t="inlineStr">
@@ -9507,7 +9507,7 @@
       </c>
       <c r="H162" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours reinstates a cancelled receipt; reversing the application of an issued receipt is the payment reversal requested by Accounting Controls and approved by the Cashiering TL.</t>
+          <t>Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -9539,7 +9539,7 @@
       </c>
       <c r="F163" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G163" s="12" t="inlineStr">
@@ -9549,7 +9549,7 @@
       </c>
       <c r="H163" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours reinstates a cancelled receipt; reversing the application of an issued receipt is the payment reversal requested by Accounting Controls and approved by the Cashiering TL.</t>
+          <t>Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -9581,7 +9581,7 @@
       </c>
       <c r="F164" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G164" s="12" t="inlineStr">
@@ -9591,7 +9591,7 @@
       </c>
       <c r="H164" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours reinstates a cancelled receipt; reversing the application of an issued receipt is the payment reversal requested by Accounting Controls and approved by the Cashiering TL.</t>
+          <t>Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -9623,7 +9623,7 @@
       </c>
       <c r="F165" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G165" s="12" t="inlineStr">
@@ -9633,7 +9633,7 @@
       </c>
       <c r="H165" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours reinstates a cancelled receipt; reversing the application of an issued receipt is the payment reversal requested by Accounting Controls and approved by the Cashiering TL.</t>
+          <t>Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -9665,7 +9665,7 @@
       </c>
       <c r="F166" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G166" s="12" t="inlineStr">
@@ -9675,7 +9675,7 @@
       </c>
       <c r="H166" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours reinstates a cancelled receipt; reversing the application of an issued receipt is the payment reversal requested by Accounting Controls and approved by the Cashiering TL.</t>
+          <t>Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -9707,7 +9707,7 @@
       </c>
       <c r="F167" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G167" s="12" t="inlineStr">
@@ -9717,7 +9717,7 @@
       </c>
       <c r="H167" s="12" t="inlineStr">
         <is>
-          <t>The CSHID.005 information is captured; reinstatement of an issued receipt by account follows decision C2.</t>
+          <t>Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -9749,7 +9749,7 @@
       </c>
       <c r="F168" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G168" s="12" t="inlineStr">
@@ -9759,7 +9759,7 @@
       </c>
       <c r="H168" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours: full or partial by amount, reason groups of the BRD and the encoded fields (invoice, AR / OR no., assured, AO, Unit Head, Team Leader).</t>
+          <t>Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -9791,7 +9791,7 @@
       </c>
       <c r="F169" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G169" s="12" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="H169" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours: full or partial by amount, reason groups of the BRD and the encoded fields (invoice, AR / OR no., assured, AO, Unit Head, Team Leader).</t>
+          <t>Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -9843,7 +9843,7 @@
       </c>
       <c r="H170" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Same maker-checker; ours numbers RIN-yyyy-n.</t>
+          <t>Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -9885,7 +9885,7 @@
       </c>
       <c r="H171" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Same maker-checker; ours numbers RIN-yyyy-n.</t>
+          <t>Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -9927,7 +9927,7 @@
       </c>
       <c r="H172" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Same maker-checker; ours numbers RIN-yyyy-n.</t>
+          <t>Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -9969,7 +9969,7 @@
       </c>
       <c r="H173" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Same maker-checker; ours numbers RIN-yyyy-n.</t>
+          <t>Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -10011,7 +10011,7 @@
       </c>
       <c r="H174" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Same maker-checker; ours numbers RIN-yyyy-n.</t>
+          <t>Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -10053,7 +10053,7 @@
       </c>
       <c r="H175" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Same maker-checker; ours numbers RIN-yyyy-n.</t>
+          <t>Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -10095,7 +10095,7 @@
       </c>
       <c r="H176" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Same maker-checker; ours numbers RIN-yyyy-n.</t>
+          <t>Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -10137,7 +10137,7 @@
       </c>
       <c r="H177" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Same maker-checker; ours numbers RIN-yyyy-n.</t>
+          <t>Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -10179,7 +10179,7 @@
       </c>
       <c r="H178" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Same maker-checker; ours numbers RIN-yyyy-n.</t>
+          <t>Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -10221,7 +10221,7 @@
       </c>
       <c r="H179" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Same maker-checker; ours numbers RIN-yyyy-n.</t>
+          <t>Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -10253,7 +10253,7 @@
       </c>
       <c r="F180" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G180" s="12" t="inlineStr">
@@ -10263,7 +10263,7 @@
       </c>
       <c r="H180" s="12" t="inlineStr">
         <is>
-          <t>Reinstatement of an issued receipt follows decision C2.</t>
+          <t>Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -10295,7 +10295,7 @@
       </c>
       <c r="F181" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G181" s="12" t="inlineStr">
@@ -10305,7 +10305,7 @@
       </c>
       <c r="H181" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours restores the receipt, posts the reinstated amount and applies it to the encoded invoice; remitted premium is handled by Adjustment (AR Insurer) for endorsements; no AP Unapplied Commission.</t>
+          <t>Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -10337,7 +10337,7 @@
       </c>
       <c r="F182" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G182" s="12" t="inlineStr">
@@ -10347,7 +10347,7 @@
       </c>
       <c r="H182" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours restores the receipt, posts the reinstated amount and applies it to the encoded invoice; remitted premium is handled by Adjustment (AR Insurer) for endorsements; no AP Unapplied Commission.</t>
+          <t>Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -10379,7 +10379,7 @@
       </c>
       <c r="F183" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G183" s="12" t="inlineStr">
@@ -10389,7 +10389,7 @@
       </c>
       <c r="H183" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours restores the receipt, posts the reinstated amount and applies it to the encoded invoice; remitted premium is handled by Adjustment (AR Insurer) for endorsements; no AP Unapplied Commission.</t>
+          <t>Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -10421,7 +10421,7 @@
       </c>
       <c r="F184" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G184" s="12" t="inlineStr">
@@ -10431,7 +10431,7 @@
       </c>
       <c r="H184" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours restores the receipt, posts the reinstated amount and applies it to the encoded invoice; remitted premium is handled by Adjustment (AR Insurer) for endorsements; no AP Unapplied Commission.</t>
+          <t>Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -10463,7 +10463,7 @@
       </c>
       <c r="F185" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G185" s="12" t="inlineStr">
@@ -10473,7 +10473,7 @@
       </c>
       <c r="H185" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours restores the receipt, posts the reinstated amount and applies it to the encoded invoice; remitted premium is handled by Adjustment (AR Insurer) for endorsements; no AP Unapplied Commission.</t>
+          <t>Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -10505,7 +10505,7 @@
       </c>
       <c r="F186" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G186" s="12" t="inlineStr">
@@ -10515,7 +10515,7 @@
       </c>
       <c r="H186" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours restores the receipt, posts the reinstated amount and applies it to the encoded invoice; remitted premium is handled by Adjustment (AR Insurer) for endorsements; no AP Unapplied Commission.</t>
+          <t>Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="H187" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours posts the reinstatement at the receipt's BOOK rate; entries given in this FRS.3.</t>
+          <t>Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -10599,7 +10599,7 @@
       </c>
       <c r="H188" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours posts the reinstatement at the receipt's BOOK rate; entries given in this FRS.3.</t>
+          <t>Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -10641,7 +10641,7 @@
       </c>
       <c r="H189" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours posts the reinstatement at the receipt's BOOK rate; entries given in this FRS.3.</t>
+          <t>Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -10683,7 +10683,7 @@
       </c>
       <c r="H190" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: -</t>
+          <t>Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -10715,7 +10715,7 @@
       </c>
       <c r="F191" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G191" s="12" t="inlineStr">
@@ -10725,7 +10725,7 @@
       </c>
       <c r="H191" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours uploads one file at a time on the tab of its type (Bills Payment, Trade, CLPC, Direct Credit, PDC).</t>
+          <t>Payment file tests: Bills Payment, CLPC, Trade, Direct Credit, post-dated check and commission schedule files in the client's layouts; name convention, size limit, duplicate file and rows, header count and total, TOTAL row; run report per category; legacy numbers as match keys; Direct Credit identification; files received via MFT with the alert of a refused file; channel simulator end to end.</t>
         </is>
       </c>
     </row>
@@ -10757,7 +10757,7 @@
       </c>
       <c r="F192" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G192" s="12" t="inlineStr">
@@ -10767,7 +10767,7 @@
       </c>
       <c r="H192" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours uploads one file at a time on the tab of its type (Bills Payment, Trade, CLPC, Direct Credit, PDC).</t>
+          <t>Payment file tests: Bills Payment, CLPC, Trade, Direct Credit, post-dated check and commission schedule files in the client's layouts; name convention, size limit, duplicate file and rows, header count and total, TOTAL row; run report per category; legacy numbers as match keys; Direct Credit identification; files received via MFT with the alert of a refused file; channel simulator end to end.</t>
         </is>
       </c>
     </row>
@@ -10799,7 +10799,7 @@
       </c>
       <c r="F193" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G193" s="12" t="inlineStr">
@@ -10809,7 +10809,7 @@
       </c>
       <c r="H193" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours uploads one file at a time on the tab of its type (Bills Payment, Trade, CLPC, Direct Credit, PDC).</t>
+          <t>Payment file tests: Bills Payment, CLPC, Trade, Direct Credit, post-dated check and commission schedule files in the client's layouts; name convention, size limit, duplicate file and rows, header count and total, TOTAL row; run report per category; legacy numbers as match keys; Direct Credit identification; files received via MFT with the alert of a refused file; channel simulator end to end.</t>
         </is>
       </c>
     </row>
@@ -10841,7 +10841,7 @@
       </c>
       <c r="F194" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G194" s="12" t="inlineStr">
@@ -10851,7 +10851,7 @@
       </c>
       <c r="H194" s="12" t="inlineStr">
         <is>
-          <t>MFT intake planned for with BDOI IT.</t>
+          <t>Payment file tests: Bills Payment, CLPC, Trade, Direct Credit, post-dated check and commission schedule files in the client's layouts; name convention, size limit, duplicate file and rows, header count and total, TOTAL row; run report per category; legacy numbers as match keys; Direct Credit identification; files received via MFT with the alert of a refused file; channel simulator end to end.</t>
         </is>
       </c>
     </row>
@@ -10883,7 +10883,7 @@
       </c>
       <c r="F195" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G195" s="12" t="inlineStr">
@@ -10893,7 +10893,7 @@
       </c>
       <c r="H195" s="12" t="inlineStr">
         <is>
-          <t>Duplicate file refusal is available; file-name check and 50 MB planned for.</t>
+          <t>Payment file tests: Bills Payment, CLPC, Trade, Direct Credit, post-dated check and commission schedule files in the client's layouts; name convention, size limit, duplicate file and rows, header count and total, TOTAL row; run report per category; legacy numbers as match keys; Direct Credit identification; files received via MFT with the alert of a refused file; channel simulator end to end.</t>
         </is>
       </c>
     </row>
@@ -10925,7 +10925,7 @@
       </c>
       <c r="F196" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G196" s="12" t="inlineStr">
@@ -10935,7 +10935,7 @@
       </c>
       <c r="H196" s="12" t="inlineStr">
         <is>
-          <t>Configurable layouts are available; header totals and the TOTAL row planned for.</t>
+          <t>Payment file tests: Bills Payment, CLPC, Trade, Direct Credit, post-dated check and commission schedule files in the client's layouts; name convention, size limit, duplicate file and rows, header count and total, TOTAL row; run report per category; legacy numbers as match keys; Direct Credit identification; files received via MFT with the alert of a refused file; channel simulator end to end.</t>
         </is>
       </c>
     </row>
@@ -10977,7 +10977,7 @@
       </c>
       <c r="H197" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours validates every row before the valid rows are processed; the holding area is a technical matter.</t>
+          <t>Payment file tests: Bills Payment, CLPC, Trade, Direct Credit, post-dated check and commission schedule files in the client's layouts; name convention, size limit, duplicate file and rows, header count and total, TOTAL row; run report per category; legacy numbers as match keys; Direct Credit identification; files received via MFT with the alert of a refused file; channel simulator end to end.</t>
         </is>
       </c>
     </row>
@@ -11009,7 +11009,7 @@
       </c>
       <c r="F198" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G198" s="12" t="inlineStr">
@@ -11019,7 +11019,7 @@
       </c>
       <c r="H198" s="12" t="inlineStr">
         <is>
-          <t>Matching on account references and pre-booked is available; legacy numbers as keys planned for.</t>
+          <t>Payment file tests: Bills Payment, CLPC, Trade, Direct Credit, post-dated check and commission schedule files in the client's layouts; name convention, size limit, duplicate file and rows, header count and total, TOTAL row; run report per category; legacy numbers as match keys; Direct Credit identification; files received via MFT with the alert of a refused file; channel simulator end to end.</t>
         </is>
       </c>
     </row>
@@ -11051,7 +11051,7 @@
       </c>
       <c r="F199" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G199" s="12" t="inlineStr">
@@ -11061,7 +11061,7 @@
       </c>
       <c r="H199" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours treats every Direct Credit row as a new payment with its own AR.</t>
+          <t>Payment file tests: Bills Payment, CLPC, Trade, Direct Credit, post-dated check and commission schedule files in the client's layouts; name convention, size limit, duplicate file and rows, header count and total, TOTAL row; run report per category; legacy numbers as match keys; Direct Credit identification; files received via MFT with the alert of a refused file; channel simulator end to end.</t>
         </is>
       </c>
     </row>
@@ -11093,7 +11093,7 @@
       </c>
       <c r="F200" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G200" s="12" t="inlineStr">
@@ -11103,7 +11103,7 @@
       </c>
       <c r="H200" s="12" t="inlineStr">
         <is>
-          <t>An AR per uploaded payment is available; the For Printing status is planned for.</t>
+          <t>Payment file tests: Bills Payment, CLPC, Trade, Direct Credit, post-dated check and commission schedule files in the client's layouts; name convention, size limit, duplicate file and rows, header count and total, TOTAL row; run report per category; legacy numbers as match keys; Direct Credit identification; files received via MFT with the alert of a refused file; channel simulator end to end.</t>
         </is>
       </c>
     </row>
@@ -11145,7 +11145,7 @@
       </c>
       <c r="H201" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: -</t>
+          <t>Payment file tests: Bills Payment, CLPC, Trade, Direct Credit, post-dated check and commission schedule files in the client's layouts; name convention, size limit, duplicate file and rows, header count and total, TOTAL row; run report per category; legacy numbers as match keys; Direct Credit identification; files received via MFT with the alert of a refused file; channel simulator end to end.</t>
         </is>
       </c>
     </row>
@@ -11177,7 +11177,7 @@
       </c>
       <c r="F202" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G202" s="12" t="inlineStr">
@@ -11187,7 +11187,7 @@
       </c>
       <c r="H202" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours reports counts per outcome and the rows with their messages; amounts per category and some columns are not listed.</t>
+          <t>Payment file tests: Bills Payment, CLPC, Trade, Direct Credit, post-dated check and commission schedule files in the client's layouts; name convention, size limit, duplicate file and rows, header count and total, TOTAL row; run report per category; legacy numbers as match keys; Direct Credit identification; files received via MFT with the alert of a refused file; channel simulator end to end.</t>
         </is>
       </c>
     </row>
@@ -11219,7 +11219,7 @@
       </c>
       <c r="F203" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G203" s="12" t="inlineStr">
@@ -11229,7 +11229,7 @@
       </c>
       <c r="H203" s="12" t="inlineStr">
         <is>
-          <t>Cashiering works the list; Marketing and Commission Receivable access follows decision C13.</t>
+          <t>Unapplied payment list test: filters by type, payment date, insurer, client, assured, account and part of the number in any case; source, account, PN and loan application numbers, client and insurer; a fully applied payment leaves the list; a Marketing user sees the payments of his or her unit only.</t>
         </is>
       </c>
     </row>
@@ -11261,7 +11261,7 @@
       </c>
       <c r="F204" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G204" s="12" t="inlineStr">
@@ -11271,7 +11271,7 @@
       </c>
       <c r="H204" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours: a Cashiering workbench; Collections asks through Incoming Requests; AR Insurer is a receivable from the insurer, not an unapplied item; no AP Unapplied Commission.</t>
+          <t>Unapplied payment list test: filters by type, payment date, insurer, client, assured, account and part of the number in any case; source, account, PN and loan application numbers, client and insurer; a fully applied payment leaves the list; a Marketing user sees the payments of his or her unit only.</t>
         </is>
       </c>
     </row>
@@ -11303,7 +11303,7 @@
       </c>
       <c r="F205" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G205" s="12" t="inlineStr">
@@ -11313,7 +11313,7 @@
       </c>
       <c r="H205" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours searches reference or payor and filters origin; columns reference, payor, client, unit, amount, balance, disposition, received, stage.</t>
+          <t>Unapplied payment list test: filters by type, payment date, insurer, client, assured, account and part of the number in any case; source, account, PN and loan application numbers, client and insurer; a fully applied payment leaves the list; a Marketing user sees the payments of his or her unit only.</t>
         </is>
       </c>
     </row>
@@ -11345,7 +11345,7 @@
       </c>
       <c r="F206" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G206" s="12" t="inlineStr">
@@ -11355,7 +11355,7 @@
       </c>
       <c r="H206" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours searches reference or payor and filters origin; columns reference, payor, client, unit, amount, balance, disposition, received, stage.</t>
+          <t>Unapplied payment list test: filters by type, payment date, insurer, client, assured, account and part of the number in any case; source, account, PN and loan application numbers, client and insurer; a fully applied payment leaves the list; a Marketing user sees the payments of his or her unit only.</t>
         </is>
       </c>
     </row>
@@ -11387,7 +11387,7 @@
       </c>
       <c r="F207" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G207" s="12" t="inlineStr">
@@ -11397,7 +11397,7 @@
       </c>
       <c r="H207" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours searches reference or payor and filters origin; columns reference, payor, client, unit, amount, balance, disposition, received, stage.</t>
+          <t>Unapplied payment list test: filters by type, payment date, insurer, client, assured, account and part of the number in any case; source, account, PN and loan application numbers, client and insurer; a fully applied payment leaves the list; a Marketing user sees the payments of his or her unit only.</t>
         </is>
       </c>
     </row>
@@ -11439,7 +11439,7 @@
       </c>
       <c r="H208" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours transfers the whole remaining balance; the unapplied item fields are listed in ours.</t>
+          <t>Unapplied payment list test: filters by type, payment date, insurer, client, assured, account and part of the number in any case; source, account, PN and loan application numbers, client and insurer; a fully applied payment leaves the list; a Marketing user sees the payments of his or her unit only.</t>
         </is>
       </c>
     </row>
@@ -11471,7 +11471,7 @@
       </c>
       <c r="F209" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G209" s="12" t="inlineStr">
@@ -11481,7 +11481,7 @@
       </c>
       <c r="H209" s="12" t="inlineStr">
         <is>
-          <t>The record holds its source, amounts and history; PN or loan application number and insurer columns planned for.</t>
+          <t>Unapplied payment list test: filters by type, payment date, insurer, client, assured, account and part of the number in any case; source, account, PN and loan application numbers, client and insurer; a fully applied payment leaves the list; a Marketing user sees the payments of his or her unit only.</t>
         </is>
       </c>
     </row>
@@ -11513,7 +11513,7 @@
       </c>
       <c r="F210" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G210" s="12" t="inlineStr">
@@ -11523,7 +11523,7 @@
       </c>
       <c r="H210" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours adds DST payment application and Others, with an approval rule per type; reclass and transfer move the whole balance.</t>
+          <t>Unapplied disposition tests: apply to another invoice through the hierarchy, refund through Disbursement with Team approval, reclass and transfer of the remaining balance, tabs per status and bulk submission and approval.</t>
         </is>
       </c>
     </row>
@@ -11565,7 +11565,7 @@
       </c>
       <c r="H211" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours adds a Done tab.</t>
+          <t>Unapplied disposition tests: apply to another invoice through the hierarchy, refund through Disbursement with Team approval, reclass and transfer of the remaining balance, tabs per status and bulk submission and approval.</t>
         </is>
       </c>
     </row>
@@ -11607,7 +11607,7 @@
       </c>
       <c r="H212" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours also re-matches every 2 hours.</t>
+          <t>Unapplied disposition tests: apply to another invoice through the hierarchy, refund through Disbursement with Team approval, reclass and transfer of the remaining balance, tabs per status and bulk submission and approval.</t>
         </is>
       </c>
     </row>
@@ -11639,7 +11639,7 @@
       </c>
       <c r="F213" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G213" s="12" t="inlineStr">
@@ -11649,7 +11649,7 @@
       </c>
       <c r="H213" s="12" t="inlineStr">
         <is>
-          <t>OR at the Disbursement approval follows decision C12; today the OR is issued at the remittance approval.</t>
+          <t>Settlement OR tests: the commission OR of an insurer settlement waits for the approval of Disbursement and is then issued, one OR per insurer and batch with one line per invoice and the OR number on the batch; a cancelled payment request cancels it; issued at the remittance approval with the other setting.</t>
         </is>
       </c>
     </row>
@@ -11681,7 +11681,7 @@
       </c>
       <c r="F214" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G214" s="12" t="inlineStr">
@@ -11691,7 +11691,7 @@
       </c>
       <c r="H214" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours issues the commission OR when the remittance batch is approved.</t>
+          <t>Settlement OR tests: the commission OR of an insurer settlement waits for the approval of Disbursement and is then issued, one OR per insurer and batch with one line per invoice and the OR number on the batch; a cancelled payment request cancels it; issued at the remittance approval with the other setting.</t>
         </is>
       </c>
     </row>
@@ -11723,7 +11723,7 @@
       </c>
       <c r="F215" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G215" s="12" t="inlineStr">
@@ -11733,7 +11733,7 @@
       </c>
       <c r="H215" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: The fields of the remittance OR are listed in ours (one line per invoice).</t>
+          <t>Settlement OR tests: the commission OR of an insurer settlement waits for the approval of Disbursement and is then issued, one OR per insurer and batch with one line per invoice and the OR number on the batch; a cancelled payment request cancels it; issued at the remittance approval with the other setting.</t>
         </is>
       </c>
     </row>
@@ -11765,7 +11765,7 @@
       </c>
       <c r="F216" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G216" s="12" t="inlineStr">
@@ -11775,7 +11775,7 @@
       </c>
       <c r="H216" s="12" t="inlineStr">
         <is>
-          <t>The remittance OR has one line per invoice; the mapping at the Disbursement approval follows C12.</t>
+          <t>Settlement OR tests: the commission OR of an insurer settlement waits for the approval of Disbursement and is then issued, one OR per insurer and batch with one line per invoice and the OR number on the batch; a cancelled payment request cancels it; issued at the remittance approval with the other setting.</t>
         </is>
       </c>
     </row>
@@ -11807,7 +11807,7 @@
       </c>
       <c r="F217" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G217" s="12" t="inlineStr">
@@ -11817,7 +11817,7 @@
       </c>
       <c r="H217" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours: one receipt search on the ten BRD criteria and Invoice 360 with components, receipts, remittances, adjustments and history; ACSL manual adjustments are not named.</t>
+          <t>Receipt search tests on the inquiry criteria, single and combined, names by part in any case, and the search log listing each search with the user and the criteria in words for the Auditor and the Team Leader. Walkthrough of the account record inquiry.</t>
         </is>
       </c>
     </row>
@@ -11849,7 +11849,7 @@
       </c>
       <c r="F218" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G218" s="12" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="H218" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours: one receipt search on the ten BRD criteria and Invoice 360 with components, receipts, remittances, adjustments and history; ACSL manual adjustments are not named.</t>
+          <t>Receipt search tests on the inquiry criteria, single and combined, names by part in any case, and the search log listing each search with the user and the criteria in words for the Auditor and the Team Leader. Walkthrough of the account record inquiry.</t>
         </is>
       </c>
     </row>
@@ -11891,7 +11891,7 @@
       </c>
       <c r="F219" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G219" s="12" t="inlineStr">
@@ -11901,7 +11901,7 @@
       </c>
       <c r="H219" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours: one receipt search on the ten BRD criteria and Invoice 360 with components, receipts, remittances, adjustments and history; ACSL manual adjustments are not named.</t>
+          <t>Receipt search tests on the inquiry criteria, single and combined, names by part in any case, and the search log listing each search with the user and the criteria in words for the Auditor and the Team Leader. Walkthrough of the account record inquiry.</t>
         </is>
       </c>
     </row>
@@ -11943,7 +11943,7 @@
       </c>
       <c r="H220" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours separates view and export rights and archives every run.</t>
+          <t>Report tests: every Cashiering report runs and exports in every format, view and export rights apart, each run archived, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;.</t>
         </is>
       </c>
     </row>
@@ -11975,7 +11975,7 @@
       </c>
       <c r="F221" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G221" s="12" t="inlineStr">
@@ -11985,7 +11985,7 @@
       </c>
       <c r="H221" s="12" t="inlineStr">
         <is>
-          <t>View and export rights and the archive are available; BDOI's file names are planned for.</t>
+          <t>Report tests: every Cashiering report runs and exports in every format, view and export rights apart, each run archived, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;.</t>
         </is>
       </c>
     </row>
@@ -12027,7 +12027,7 @@
       </c>
       <c r="H222" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours separates view and export rights and archives every run.</t>
+          <t>Report tests: every Cashiering report runs and exports in every format, view and export rights apart, each run archived, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;.</t>
         </is>
       </c>
     </row>
@@ -12069,7 +12069,7 @@
       </c>
       <c r="H223" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours separates view and export rights and archives every run.</t>
+          <t>Report tests: every Cashiering report runs and exports in every format, view and export rights apart, each run archived, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;.</t>
         </is>
       </c>
     </row>
@@ -12101,7 +12101,7 @@
       </c>
       <c r="F224" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G224" s="12" t="inlineStr">
@@ -12111,7 +12111,7 @@
       </c>
       <c r="H224" s="12" t="inlineStr">
         <is>
-          <t>Report layouts of BDOI's list are being aligned; 12 layouts are draft.</t>
+          <t>Report tests: columns in the client's order with totals, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;, ageing brackets 0-30 to above 365, payment reversals with record, reason, creator and poster, summary per disposition, certification of payment with its series number.</t>
         </is>
       </c>
     </row>
@@ -12143,7 +12143,7 @@
       </c>
       <c r="F225" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G225" s="12" t="inlineStr">
@@ -12153,7 +12153,7 @@
       </c>
       <c r="H225" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours lacks bank, branch and check no.; BDOI's rule asks “Payment to Premium (manual?)”.</t>
+          <t>Report tests: columns in the client's order with totals, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;, ageing brackets 0-30 to above 365, payment reversals with record, reason, creator and poster, summary per disposition, certification of payment with its series number.</t>
         </is>
       </c>
     </row>
@@ -12195,7 +12195,7 @@
       </c>
       <c r="H226" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: -</t>
+          <t>Report tests: columns in the client's order with totals, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;, ageing brackets 0-30 to above 365, payment reversals with record, reason, creator and poster, summary per disposition, certification of payment with its series number.</t>
         </is>
       </c>
     </row>
@@ -12237,7 +12237,7 @@
       </c>
       <c r="H227" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Same fields; ours lists the minimal excess payments only.</t>
+          <t>Report tests: columns in the client's order with totals, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;, ageing brackets 0-30 to above 365, payment reversals with record, reason, creator and poster, summary per disposition, certification of payment with its series number.</t>
         </is>
       </c>
     </row>
@@ -12269,7 +12269,7 @@
       </c>
       <c r="F228" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G228" s="12" t="inlineStr">
@@ -12279,7 +12279,7 @@
       </c>
       <c r="H228" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours has no reason column.</t>
+          <t>Report tests: columns in the client's order with totals, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;, ageing brackets 0-30 to above 365, payment reversals with record, reason, creator and poster, summary per disposition, certification of payment with its series number.</t>
         </is>
       </c>
     </row>
@@ -12321,7 +12321,7 @@
       </c>
       <c r="H229" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: BDOI's rule says “Extract all cancelled OR” (typing error).</t>
+          <t>Report tests: columns in the client's order with totals, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;, ageing brackets 0-30 to above 365, payment reversals with record, reason, creator and poster, summary per disposition, certification of payment with its series number.</t>
         </is>
       </c>
     </row>
@@ -12353,7 +12353,7 @@
       </c>
       <c r="F230" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G230" s="12" t="inlineStr">
@@ -12363,7 +12363,7 @@
       </c>
       <c r="H230" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Layout draft in ours.</t>
+          <t>Report tests: columns in the client's order with totals, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;, ageing brackets 0-30 to above 365, payment reversals with record, reason, creator and poster, summary per disposition, certification of payment with its series number.</t>
         </is>
       </c>
     </row>
@@ -12395,7 +12395,7 @@
       </c>
       <c r="F231" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G231" s="12" t="inlineStr">
@@ -12405,7 +12405,7 @@
       </c>
       <c r="H231" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Layout draft in ours; the criteria are not defined in either.</t>
+          <t>Report tests: columns in the client's order with totals, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;, ageing brackets 0-30 to above 365, payment reversals with record, reason, creator and poster, summary per disposition, certification of payment with its series number.</t>
         </is>
       </c>
     </row>
@@ -12437,7 +12437,7 @@
       </c>
       <c r="F232" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G232" s="12" t="inlineStr">
@@ -12447,7 +12447,7 @@
       </c>
       <c r="H232" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Layout draft in ours; BDOI's rule uses 1.00 where ours uses 10.00.</t>
+          <t>Report tests: columns in the client's order with totals, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;, ageing brackets 0-30 to above 365, payment reversals with record, reason, creator and poster, summary per disposition, certification of payment with its series number.</t>
         </is>
       </c>
     </row>
@@ -12479,7 +12479,7 @@
       </c>
       <c r="F233" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G233" s="12" t="inlineStr">
@@ -12489,7 +12489,7 @@
       </c>
       <c r="H233" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Layout draft in ours; the commission rule is inactive until BDOI confirms it.</t>
+          <t>Report tests: columns in the client's order with totals, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;, ageing brackets 0-30 to above 365, payment reversals with record, reason, creator and poster, summary per disposition, certification of payment with its series number.</t>
         </is>
       </c>
     </row>
@@ -12521,7 +12521,7 @@
       </c>
       <c r="F234" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G234" s="12" t="inlineStr">
@@ -12531,7 +12531,7 @@
       </c>
       <c r="H234" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Layout draft in ours; BDOI lists OR numbers only (no AR).</t>
+          <t>Report tests: columns in the client's order with totals, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;, ageing brackets 0-30 to above 365, payment reversals with record, reason, creator and poster, summary per disposition, certification of payment with its series number.</t>
         </is>
       </c>
     </row>
@@ -12563,7 +12563,7 @@
       </c>
       <c r="F235" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G235" s="12" t="inlineStr">
@@ -12573,7 +12573,7 @@
       </c>
       <c r="H235" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours names it “Advance Payment Transactions (Auto-Credit)”, layout draft.</t>
+          <t>Report tests: columns in the client's order with totals, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;, ageing brackets 0-30 to above 365, payment reversals with record, reason, creator and poster, summary per disposition, certification of payment with its series number.</t>
         </is>
       </c>
     </row>
@@ -12605,7 +12605,7 @@
       </c>
       <c r="F236" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G236" s="12" t="inlineStr">
@@ -12615,7 +12615,7 @@
       </c>
       <c r="H236" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Layout draft in ours.</t>
+          <t>Report tests: columns in the client's order with totals, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;, ageing brackets 0-30 to above 365, payment reversals with record, reason, creator and poster, summary per disposition, certification of payment with its series number.</t>
         </is>
       </c>
     </row>
@@ -12647,7 +12647,7 @@
       </c>
       <c r="F237" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G237" s="12" t="inlineStr">
@@ -12657,7 +12657,7 @@
       </c>
       <c r="H237" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Layout draft in ours.</t>
+          <t>Report tests: columns in the client's order with totals, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;, ageing brackets 0-30 to above 365, payment reversals with record, reason, creator and poster, summary per disposition, certification of payment with its series number.</t>
         </is>
       </c>
     </row>
@@ -12689,7 +12689,7 @@
       </c>
       <c r="F238" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G238" s="12" t="inlineStr">
@@ -12699,7 +12699,7 @@
       </c>
       <c r="H238" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Layout draft in ours.</t>
+          <t>Report tests: columns in the client's order with totals, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;, ageing brackets 0-30 to above 365, payment reversals with record, reason, creator and poster, summary per disposition, certification of payment with its series number.</t>
         </is>
       </c>
     </row>
@@ -12731,7 +12731,7 @@
       </c>
       <c r="F239" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G239" s="12" t="inlineStr">
@@ -12741,7 +12741,7 @@
       </c>
       <c r="H239" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours has no series number of the certificate.</t>
+          <t>Report tests: columns in the client's order with totals, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;, ageing brackets 0-30 to above 365, payment reversals with record, reason, creator and poster, summary per disposition, certification of payment with its series number.</t>
         </is>
       </c>
     </row>
@@ -12773,7 +12773,7 @@
       </c>
       <c r="F240" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G240" s="12" t="inlineStr">
@@ -12783,7 +12783,7 @@
       </c>
       <c r="H240" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Layout draft in ours.</t>
+          <t>Report tests: columns in the client's order with totals, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;, ageing brackets 0-30 to above 365, payment reversals with record, reason, creator and poster, summary per disposition, certification of payment with its series number.</t>
         </is>
       </c>
     </row>
@@ -12815,7 +12815,7 @@
       </c>
       <c r="F241" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G241" s="12" t="inlineStr">
@@ -12825,7 +12825,7 @@
       </c>
       <c r="H241" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Layout draft in ours.</t>
+          <t>Report tests: columns in the client's order with totals, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;, ageing brackets 0-30 to above 365, payment reversals with record, reason, creator and poster, summary per disposition, certification of payment with its series number.</t>
         </is>
       </c>
     </row>
@@ -12857,7 +12857,7 @@
       </c>
       <c r="F242" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G242" s="12" t="inlineStr">
@@ -12867,7 +12867,7 @@
       </c>
       <c r="H242" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: No such report in ours; the disposition values differ from our disposition types.</t>
+          <t>Report tests: columns in the client's order with totals, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;, ageing brackets 0-30 to above 365, payment reversals with record, reason, creator and poster, summary per disposition, certification of payment with its series number.</t>
         </is>
       </c>
     </row>
@@ -12993,7 +12993,7 @@
       </c>
       <c r="H245" s="12" t="inlineStr">
         <is>
-          <t>Shown working in the end-to-end run; criteria without an automated check are confirmed in UAT.</t>
+          <t>Cashiering dashboard test: count and amount per receipt type and status for issuance, cancellation, reinstatement, returned records, unapplied payments and payment files; each item opens its list; shown within 5 seconds.</t>
         </is>
       </c>
     </row>
@@ -13035,7 +13035,7 @@
       </c>
       <c r="H246" s="12" t="inlineStr">
         <is>
-          <t>Shown working in the end-to-end run; criteria without an automated check are confirmed in UAT.</t>
+          <t>Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -13067,7 +13067,7 @@
       </c>
       <c r="F247" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G247" s="12" t="inlineStr">
@@ -13077,7 +13077,7 @@
       </c>
       <c r="H247" s="12" t="inlineStr">
         <is>
-          <t>The receipts of the day are listed with their status; the totals per bank account are planned for.</t>
+          <t>Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -13119,7 +13119,7 @@
       </c>
       <c r="H248" s="12" t="inlineStr">
         <is>
-          <t>Shown working in the end-to-end run; criteria without an automated check are confirmed in UAT.</t>
+          <t>OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -13161,7 +13161,7 @@
       </c>
       <c r="H249" s="12" t="inlineStr">
         <is>
-          <t>Shown working in the end-to-end run; criteria without an automated check are confirmed in UAT.</t>
+          <t>Receipt series tests: series per receipting branch with its year and number format (prefix, year, branch indicator, sequence), authorised by another user, warning alert of the numbers left, OR series for Head Office only, end below the last number refused.</t>
         </is>
       </c>
     </row>
@@ -13193,7 +13193,7 @@
       </c>
       <c r="F250" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G250" s="12" t="inlineStr">
@@ -13203,7 +13203,7 @@
       </c>
       <c r="H250" s="12" t="inlineStr">
         <is>
-          <t>Copy label planned for with BDOI's forms (C16).</t>
+          <t>Receipt printing tests: print by branch or insurer and issue dates, print queue of the receipts the system generated, re-print by part of the number with the REPRINT mark and the print count, certificate number at the first print, Client's and company copies with the company copy kept on the receipt, ZIP of one PDF per receipt, at most 500 per batch, retry and skip in the print log. Walkthrough of the print preview.</t>
         </is>
       </c>
     </row>
@@ -13245,7 +13245,7 @@
       </c>
       <c r="H251" s="12" t="inlineStr">
         <is>
-          <t>Shown working in the end-to-end run; criteria without an automated check are confirmed in UAT.</t>
+          <t>Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -13277,7 +13277,7 @@
       </c>
       <c r="F252" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G252" s="12" t="inlineStr">
@@ -13287,7 +13287,7 @@
       </c>
       <c r="H252" s="12" t="inlineStr">
         <is>
-          <t>The Certification of Payment PDF is available; its series number is planned for.</t>
+          <t>Receipt form tests: AR and OR forms with the company address and VAT TIN, the amount in words and in figures, footer lines and copy label; a form change printed only after another user approved it. Certification of Payment test with its series number.</t>
         </is>
       </c>
     </row>
@@ -13329,7 +13329,7 @@
       </c>
       <c r="H253" s="12" t="inlineStr">
         <is>
-          <t>Shown working in the end-to-end run; criteria without an automated check are confirmed in UAT.</t>
+          <t>Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -13371,7 +13371,7 @@
       </c>
       <c r="H254" s="12" t="inlineStr">
         <is>
-          <t>Shown working in the end-to-end run; criteria without an automated check are confirmed in UAT.</t>
+          <t>Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -13413,7 +13413,7 @@
       </c>
       <c r="H255" s="12" t="inlineStr">
         <is>
-          <t>Shown working in the end-to-end run; criteria without an automated check are confirmed in UAT.</t>
+          <t>Payment file tests: Bills Payment, CLPC, Trade, Direct Credit, post-dated check and commission schedule files in the client's layouts; name convention, size limit, duplicate file and rows, header count and total, TOTAL row; run report per category; legacy numbers as match keys; Direct Credit identification; files received via MFT with the alert of a refused file; channel simulator end to end.</t>
         </is>
       </c>
     </row>
@@ -13455,7 +13455,7 @@
       </c>
       <c r="H256" s="12" t="inlineStr">
         <is>
-          <t>Shown working in the end-to-end run; criteria without an automated check are confirmed in UAT.</t>
+          <t>Unapplied payment list test: filters by type, payment date, insurer, client, assured, account and part of the number in any case; source, account, PN and loan application numbers, client and insurer; a fully applied payment leaves the list; a Marketing user sees the payments of his or her unit only.</t>
         </is>
       </c>
     </row>
@@ -13497,7 +13497,7 @@
       </c>
       <c r="H257" s="12" t="inlineStr">
         <is>
-          <t>Shown working in the end-to-end run; criteria without an automated check are confirmed in UAT.</t>
+          <t>Settlement OR tests: the commission OR of an insurer settlement waits for the approval of Disbursement and is then issued, one OR per insurer and batch with one line per invoice and the OR number on the batch; a cancelled payment request cancels it; issued at the remittance approval with the other setting.</t>
         </is>
       </c>
     </row>
@@ -13529,7 +13529,7 @@
       </c>
       <c r="F258" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G258" s="12" t="inlineStr">
@@ -13539,7 +13539,7 @@
       </c>
       <c r="H258" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours: one receipt search on the ten BRD criteria and Invoice 360 with components, receipts, remittances, adjustments and history; ACSL manual adjustments are not named.</t>
+          <t>Receipt search tests on the inquiry criteria, single and combined, names by part in any case, and the search log listing each search with the user and the criteria in words for the Auditor and the Team Leader. Walkthrough of the account record inquiry.</t>
         </is>
       </c>
     </row>
@@ -13581,7 +13581,7 @@
       </c>
       <c r="H259" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours separates view and export rights and archives every run.</t>
+          <t>Report tests: every Cashiering report runs and exports in every format, view and export rights apart, each run archived, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;.</t>
         </is>
       </c>
     </row>
@@ -13623,7 +13623,7 @@
       </c>
       <c r="H260" s="12" t="inlineStr">
         <is>
-          <t>Shown working in the end-to-end run; criteria without an automated check are confirmed in UAT.</t>
+          <t>Report tests: columns in the client's order with totals, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;, ageing brackets 0-30 to above 365, payment reversals with record, reason, creator and poster, summary per disposition, certification of payment with its series number.</t>
         </is>
       </c>
     </row>
@@ -13665,7 +13665,7 @@
       </c>
       <c r="H261" s="12" t="inlineStr">
         <is>
-          <t>Shown working in the end-to-end run; criteria without an automated check are confirmed in UAT.</t>
+          <t>Report tests: columns in the client's order with totals, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;, ageing brackets 0-30 to above 365, payment reversals with record, reason, creator and poster, summary per disposition, certification of payment with its series number.</t>
         </is>
       </c>
     </row>
@@ -13697,7 +13697,7 @@
       </c>
       <c r="F262" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G262" s="12" t="inlineStr">
@@ -13707,7 +13707,7 @@
       </c>
       <c r="H262" s="12" t="inlineStr">
         <is>
-          <t>Layout draft.</t>
+          <t>Report tests: columns in the client's order with totals, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;, ageing brackets 0-30 to above 365, payment reversals with record, reason, creator and poster, summary per disposition, certification of payment with its series number.</t>
         </is>
       </c>
     </row>
@@ -13739,7 +13739,7 @@
       </c>
       <c r="F263" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G263" s="12" t="inlineStr">
@@ -13749,7 +13749,7 @@
       </c>
       <c r="H263" s="12" t="inlineStr">
         <is>
-          <t>Ageing brackets of BDOI planned for.</t>
+          <t>Report tests: columns in the client's order with totals, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;, ageing brackets 0-30 to above 365, payment reversals with record, reason, creator and poster, summary per disposition, certification of payment with its series number.</t>
         </is>
       </c>
     </row>
@@ -13791,7 +13791,7 @@
       </c>
       <c r="H264" s="12" t="inlineStr">
         <is>
-          <t>Shown working in the end-to-end run; criteria without an automated check are confirmed in UAT.</t>
+          <t>Report tests: columns in the client's order with totals, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;, ageing brackets 0-30 to above 365, payment reversals with record, reason, creator and poster, summary per disposition, certification of payment with its series number.</t>
         </is>
       </c>
     </row>
@@ -14379,7 +14379,7 @@
       </c>
       <c r="H278" s="12" t="inlineStr">
         <is>
-          <t>Shown working in the end-to-end run; criteria without an automated check are confirmed in UAT.</t>
+          <t>Payment file test: a file received via MFT and refused raises the alert to the Cashiering Team Leader; receipt series and pre-booked alerts.</t>
         </is>
       </c>
     </row>
@@ -14411,7 +14411,7 @@
       </c>
       <c r="F279" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G279" s="12" t="inlineStr">
@@ -14421,7 +14421,7 @@
       </c>
       <c r="H279" s="12" t="inlineStr">
         <is>
-          <t>Series and pre-booked alerts are available; the alert for a refused MFT file is planned for.</t>
+          <t>Payment file test: a file received via MFT and refused raises the alert to the Cashiering Team Leader; receipt series and pre-booked alerts.</t>
         </is>
       </c>
     </row>
@@ -14553,7 +14553,7 @@
       </c>
       <c r="E5" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F5" s="12" t="inlineStr">
@@ -14563,7 +14563,7 @@
       </c>
       <c r="G5" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours does not restrict the device; the BRD asks for the same performance on mobile and desktop.</t>
+          <t>Available: Device access test: with the device restriction set on, only the company networks and the company-issued devices reach the sign-in; the setting is off for SIT. Walkthrough on the browser of a laptop and of a tablet with the same screens.</t>
         </is>
       </c>
     </row>
@@ -14588,7 +14588,7 @@
       </c>
       <c r="E6" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F6" s="12" t="inlineStr">
@@ -14598,7 +14598,7 @@
       </c>
       <c r="G6" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours does not restrict the device; the BRD asks for the same performance on mobile and desktop.</t>
+          <t>Available: Device access test: with the device restriction set on, only the company networks and the company-issued devices reach the sign-in; the setting is off for SIT. Walkthrough on the browser of a laptop and of a tablet with the same screens.</t>
         </is>
       </c>
     </row>
@@ -14763,7 +14763,7 @@
       </c>
       <c r="E11" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F11" s="12" t="inlineStr">
@@ -14773,7 +14773,7 @@
       </c>
       <c r="G11" s="12" t="inlineStr">
         <is>
-          <t>Live counts per queue are available; the amounts per receipt type and status are planned for (C1 decides the posting items).</t>
+          <t>Available: Cashiering dashboard test: count and amount per receipt type and status for issuance, cancellation, reinstatement, returned records, unapplied payments and payment files; each item opens its list; shown within 5 seconds.</t>
         </is>
       </c>
     </row>
@@ -14798,7 +14798,7 @@
       </c>
       <c r="E12" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F12" s="12" t="inlineStr">
@@ -14808,7 +14808,7 @@
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>Live counts per queue are available; the amounts per receipt type and status are planned for (C1 decides the posting items).</t>
+          <t>Available: Cashiering dashboard test: count and amount per receipt type and status for issuance, cancellation, reinstatement, returned records, unapplied payments and payment files; each item opens its list; shown within 5 seconds.</t>
         </is>
       </c>
     </row>
@@ -14833,7 +14833,7 @@
       </c>
       <c r="E13" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
@@ -14843,7 +14843,7 @@
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>Live counts per queue are available; the amounts per receipt type and status are planned for (C1 decides the posting items).</t>
+          <t>Available: Cashiering dashboard test: count and amount per receipt type and status for issuance, cancellation, reinstatement, returned records, unapplied payments and payment files; each item opens its list; shown within 5 seconds.</t>
         </is>
       </c>
     </row>
@@ -14868,7 +14868,7 @@
       </c>
       <c r="E14" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
@@ -14878,7 +14878,7 @@
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours lists receipts and unapplied payments with filters; BDOI's columns (creation record number, receipt type, account / invoice, client, insurer) are partly shown.</t>
+          <t>Available: Cashiering dashboard test: count and amount per receipt type and status for issuance, cancellation, reinstatement, returned records, unapplied payments and payment files; each item opens its list; shown within 5 seconds.</t>
         </is>
       </c>
     </row>
@@ -14903,7 +14903,7 @@
       </c>
       <c r="E15" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
@@ -14913,7 +14913,7 @@
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours lists receipts and unapplied payments with filters; BDOI's columns (creation record number, receipt type, account / invoice, client, insurer) are partly shown.</t>
+          <t>Available: Cashiering dashboard test: count and amount per receipt type and status for issuance, cancellation, reinstatement, returned records, unapplied payments and payment files; each item opens its list; shown within 5 seconds.</t>
         </is>
       </c>
     </row>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="E16" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
@@ -14948,7 +14948,7 @@
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours has the AR class (channels and non-premium types), payor, references, amount, currency, mode, check no. and bank, payment date. Not in ours: entry type, bank account to post to, receipting branch choice (ours uses the user's branch), the 1B limit, remarks.</t>
+          <t>Available: Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -14973,7 +14973,7 @@
       </c>
       <c r="E17" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
@@ -14983,7 +14983,7 @@
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>Payor, references, currency, mode and matching are available; entry type, bank account and receipting branch are planned for.</t>
+          <t>Available: Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -15008,7 +15008,7 @@
       </c>
       <c r="E18" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
@@ -15018,7 +15018,7 @@
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>Payor, references, currency, mode and matching are available; entry type, bank account and receipting branch are planned for.</t>
+          <t>Available: Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -15043,7 +15043,7 @@
       </c>
       <c r="E19" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
@@ -15053,7 +15053,7 @@
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>Payor, references, currency, mode and matching are available; entry type, bank account and receipting branch are planned for.</t>
+          <t>Available: Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -15078,7 +15078,7 @@
       </c>
       <c r="E20" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
@@ -15088,7 +15088,7 @@
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>Payor, references, currency, mode and matching are available; entry type, bank account and receipting branch are planned for.</t>
+          <t>Available: Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -15113,7 +15113,7 @@
       </c>
       <c r="E21" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
@@ -15123,7 +15123,7 @@
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours previews each invoice by component with the amount applied, the 2% CWT withheld and the excess; the payment is applied oldest first, not split per account by the user.</t>
+          <t>Available: Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -15148,7 +15148,7 @@
       </c>
       <c r="E22" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
@@ -15158,7 +15158,7 @@
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours previews each invoice by component with the amount applied, the 2% CWT withheld and the excess; the payment is applied oldest first, not split per account by the user.</t>
+          <t>Available: Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -15183,7 +15183,7 @@
       </c>
       <c r="E23" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
@@ -15193,7 +15193,7 @@
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>Mandatory fields and amount checks are available; the currency and check-date checks are planned for (C7).</t>
+          <t>Available: Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -15218,7 +15218,7 @@
       </c>
       <c r="E24" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
@@ -15228,7 +15228,7 @@
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>Mandatory fields and amount checks are available; the currency and check-date checks are planned for (C7).</t>
+          <t>Available: Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -15253,7 +15253,7 @@
       </c>
       <c r="E25" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
@@ -15263,7 +15263,7 @@
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>Mandatory fields and amount checks are available; the currency and check-date checks are planned for (C7).</t>
+          <t>Available: Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -15288,7 +15288,7 @@
       </c>
       <c r="E26" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
@@ -15298,7 +15298,7 @@
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>Mandatory fields and amount checks are available; the currency and check-date checks are planned for (C7).</t>
+          <t>Available: Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -15323,7 +15323,7 @@
       </c>
       <c r="E27" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
@@ -15333,7 +15333,7 @@
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>The creation record numbers follow the posting step (C1, C3).</t>
+          <t>Available: Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -15358,7 +15358,7 @@
       </c>
       <c r="E28" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
@@ -15368,7 +15368,7 @@
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>The creation record numbers follow the posting step (C1, C3).</t>
+          <t>Available: Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -15393,7 +15393,7 @@
       </c>
       <c r="E29" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
@@ -15403,7 +15403,7 @@
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>Posting step planned for after decision C1.</t>
+          <t>Available: Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -15428,7 +15428,7 @@
       </c>
       <c r="E30" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
@@ -15438,7 +15438,7 @@
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>Posting step planned for after decision C1.</t>
+          <t>Available: Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -15473,7 +15473,7 @@
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -15508,7 +15508,7 @@
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -15533,7 +15533,7 @@
       </c>
       <c r="E33" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
@@ -15543,7 +15543,7 @@
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours: OR type (service fee, profit share, commission, incentive, others), payor, currency, mode, gross, VAT, withholding tax, 2307 certificate ref.; no bank account and no entry type.</t>
+          <t>Available: OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -15568,7 +15568,7 @@
       </c>
       <c r="E34" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
@@ -15578,7 +15578,7 @@
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours: OR type (service fee, profit share, commission, incentive, others), payor, currency, mode, gross, VAT, withholding tax, 2307 certificate ref.; no bank account and no entry type.</t>
+          <t>Available: OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -15603,7 +15603,7 @@
       </c>
       <c r="E35" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
@@ -15613,7 +15613,7 @@
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours: OR type (service fee, profit share, commission, incentive, others), payor, currency, mode, gross, VAT, withholding tax, 2307 certificate ref.; no bank account and no entry type.</t>
+          <t>Available: OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -15638,7 +15638,7 @@
       </c>
       <c r="E36" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
@@ -15648,7 +15648,7 @@
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
-          <t>Duplicate refusal and the validation of the commission payment details are available; the .csv pipe template and 50 MB limit are planned for.</t>
+          <t>Available: OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -15673,7 +15673,7 @@
       </c>
       <c r="E37" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
@@ -15683,7 +15683,7 @@
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>Duplicate refusal and the validation of the commission payment details are available; the .csv pipe template and 50 MB limit are planned for.</t>
+          <t>Available: OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -15708,7 +15708,7 @@
       </c>
       <c r="E38" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
@@ -15718,7 +15718,7 @@
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
-          <t>Duplicate refusal and the validation of the commission payment details are available; the .csv pipe template and 50 MB limit are planned for.</t>
+          <t>Available: OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -15753,7 +15753,7 @@
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -15778,7 +15778,7 @@
       </c>
       <c r="E40" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
@@ -15788,7 +15788,7 @@
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
-          <t>Selection of the SOA or fee invoice is planned for.</t>
+          <t>Available: Other income test: an incentive OR lists the Valid for Collection SOAs of the insurer with their outstanding amounts, a fee OR the fee invoices of the client; the outstanding amount falls once the OR is posted.</t>
         </is>
       </c>
     </row>
@@ -15813,7 +15813,7 @@
       </c>
       <c r="E41" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
@@ -15823,7 +15823,7 @@
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>One OR per insurer and certificate is available; the exact amount match and whole-file rule follow decision C10.</t>
+          <t>Available: OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -15848,7 +15848,7 @@
       </c>
       <c r="E42" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F42" s="12" t="inlineStr">
@@ -15858,7 +15858,7 @@
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
-          <t>One OR per insurer and certificate is available; the exact amount match and whole-file rule follow decision C10.</t>
+          <t>Available: OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -15883,7 +15883,7 @@
       </c>
       <c r="E43" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
@@ -15893,7 +15893,7 @@
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours keeps a series per kind and branch with prefix, range, BIR ATP no. and warning level, authorised by a second user; no year field (the prefix can carry it).</t>
+          <t>Available: Receipt series tests: series per receipting branch with its year and number format (prefix, year, branch indicator, sequence), authorised by another user, warning alert of the numbers left, OR series for Head Office only, end below the last number refused.</t>
         </is>
       </c>
     </row>
@@ -15918,7 +15918,7 @@
       </c>
       <c r="E44" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F44" s="12" t="inlineStr">
@@ -15928,7 +15928,7 @@
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours keeps a series per kind and branch with prefix, range, BIR ATP no. and warning level, authorised by a second user; no year field (the prefix can carry it).</t>
+          <t>Available: Receipt series tests: series per receipting branch with its year and number format (prefix, year, branch indicator, sequence), authorised by another user, warning alert of the numbers left, OR series for Head Office only, end below the last number refused.</t>
         </is>
       </c>
     </row>
@@ -15953,7 +15953,7 @@
       </c>
       <c r="E45" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F45" s="12" t="inlineStr">
@@ -15963,7 +15963,7 @@
       </c>
       <c r="G45" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours keeps a series per kind and branch with prefix, range, BIR ATP no. and warning level, authorised by a second user; no year field (the prefix can carry it).</t>
+          <t>Available: Receipt series tests: series per receipting branch with its year and number format (prefix, year, branch indicator, sequence), authorised by another user, warning alert of the numbers left, OR series for Head Office only, end below the last number refused.</t>
         </is>
       </c>
     </row>
@@ -15988,7 +15988,7 @@
       </c>
       <c r="E46" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F46" s="12" t="inlineStr">
@@ -15998,7 +15998,7 @@
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours keeps a series per kind and branch with prefix, range, BIR ATP no. and warning level, authorised by a second user; no year field (the prefix can carry it).</t>
+          <t>Available: Receipt series tests: series per receipting branch with its year and number format (prefix, year, branch indicator, sequence), authorised by another user, warning alert of the numbers left, OR series for Head Office only, end below the last number refused.</t>
         </is>
       </c>
     </row>
@@ -16023,7 +16023,7 @@
       </c>
       <c r="E47" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F47" s="12" t="inlineStr">
@@ -16033,7 +16033,7 @@
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours keeps a series per kind and branch with prefix, range, BIR ATP no. and warning level, authorised by a second user; no year field (the prefix can carry it).</t>
+          <t>Available: Receipt series tests: series per receipting branch with its year and number format (prefix, year, branch indicator, sequence), authorised by another user, warning alert of the numbers left, OR series for Head Office only, end below the last number refused.</t>
         </is>
       </c>
     </row>
@@ -16058,7 +16058,7 @@
       </c>
       <c r="E48" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F48" s="12" t="inlineStr">
@@ -16068,7 +16068,7 @@
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours keeps a series per kind and branch with prefix, range, BIR ATP no. and warning level, authorised by a second user; no year field (the prefix can carry it).</t>
+          <t>Available: Receipt series tests: series per receipting branch with its year and number format (prefix, year, branch indicator, sequence), authorised by another user, warning alert of the numbers left, OR series for Head Office only, end below the last number refused.</t>
         </is>
       </c>
     </row>
@@ -16093,7 +16093,7 @@
       </c>
       <c r="E49" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
@@ -16103,7 +16103,7 @@
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
-          <t>Selection by filter is available; the print queue of system receipts is planned for.</t>
+          <t>Available: Receipt printing tests: print by branch or insurer and issue dates, print queue of the receipts the system generated, re-print by part of the number with the REPRINT mark and the print count, certificate number at the first print, Client's and company copies with the company copy kept on the receipt, ZIP of one PDF per receipt, at most 500 per batch, retry and skip in the print log. Walkthrough of the print preview.</t>
         </is>
       </c>
     </row>
@@ -16128,7 +16128,7 @@
       </c>
       <c r="E50" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F50" s="12" t="inlineStr">
@@ -16138,7 +16138,7 @@
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours filters by kind, insurer and dates, up to 500 receipts per batch; the FR names the BDOI location but the screen has no branch filter; no separate re-print search.</t>
+          <t>Available: Receipt printing tests: print by branch or insurer and issue dates, print queue of the receipts the system generated, re-print by part of the number with the REPRINT mark and the print count, certificate number at the first print, Client's and company copies with the company copy kept on the receipt, ZIP of one PDF per receipt, at most 500 per batch, retry and skip in the print log. Walkthrough of the print preview.</t>
         </is>
       </c>
     </row>
@@ -16163,7 +16163,7 @@
       </c>
       <c r="E51" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
@@ -16173,7 +16173,7 @@
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
-          <t>Certificate number planned for (C4).</t>
+          <t>Available: Receipt printing tests: print by branch or insurer and issue dates, print queue of the receipts the system generated, re-print by part of the number with the REPRINT mark and the print count, certificate number at the first print, Client's and company copies with the company copy kept on the receipt, ZIP of one PDF per receipt, at most 500 per batch, retry and skip in the print log. Walkthrough of the print preview.</t>
         </is>
       </c>
     </row>
@@ -16198,7 +16198,7 @@
       </c>
       <c r="E52" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F52" s="12" t="inlineStr">
@@ -16208,7 +16208,7 @@
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
-          <t>The print count is kept; the REPRINT mark is planned for.</t>
+          <t>Available: Receipt printing tests: print by branch or insurer and issue dates, print queue of the receipts the system generated, re-print by part of the number with the REPRINT mark and the print count, certificate number at the first print, Client's and company copies with the company copy kept on the receipt, ZIP of one PDF per receipt, at most 500 per batch, retry and skip in the print log. Walkthrough of the print preview.</t>
         </is>
       </c>
     </row>
@@ -16243,7 +16243,7 @@
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: Receipt printing tests: print by branch or insurer and issue dates, print queue of the receipts the system generated, re-print by part of the number with the REPRINT mark and the print count, certificate number at the first print, Client's and company copies with the company copy kept on the receipt, ZIP of one PDF per receipt, at most 500 per batch, retry and skip in the print log. Walkthrough of the print preview.</t>
         </is>
       </c>
     </row>
@@ -16278,7 +16278,7 @@
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: Receipt printing tests: print by branch or insurer and issue dates, print queue of the receipts the system generated, re-print by part of the number with the REPRINT mark and the print count, certificate number at the first print, Client's and company copies with the company copy kept on the receipt, ZIP of one PDF per receipt, at most 500 per batch, retry and skip in the print log. Walkthrough of the print preview.</t>
         </is>
       </c>
     </row>
@@ -16303,7 +16303,7 @@
       </c>
       <c r="E55" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr">
@@ -16313,7 +16313,7 @@
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
-          <t>Posting step planned for after decision C1.</t>
+          <t>Available: Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -16338,7 +16338,7 @@
       </c>
       <c r="E56" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F56" s="12" t="inlineStr">
@@ -16348,7 +16348,7 @@
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
-          <t>Posting step planned for after decision C1.</t>
+          <t>Available: Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -16373,7 +16373,7 @@
       </c>
       <c r="E57" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
@@ -16383,7 +16383,7 @@
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
-          <t>Posting step planned for after decision C1.</t>
+          <t>Available: Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -16408,7 +16408,7 @@
       </c>
       <c r="E58" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F58" s="12" t="inlineStr">
@@ -16418,7 +16418,7 @@
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
-          <t>Return of a creation record follows the posting step (C1).</t>
+          <t>Available: Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -16443,7 +16443,7 @@
       </c>
       <c r="E59" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F59" s="12" t="inlineStr">
@@ -16453,7 +16453,7 @@
       </c>
       <c r="G59" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours guarantees no duplicates; a sequence without gaps is not stated.</t>
+          <t>Available: Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -16488,7 +16488,7 @@
       </c>
       <c r="G60" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -16523,7 +16523,7 @@
       </c>
       <c r="G61" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -16548,7 +16548,7 @@
       </c>
       <c r="E62" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F62" s="12" t="inlineStr">
@@ -16558,7 +16558,7 @@
       </c>
       <c r="G62" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours inserts FST after LGT; check before cash is open. BDOI's review comment: “Confirm first with Insurers for payment hierarchy”.</t>
+          <t>Available: Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -16583,7 +16583,7 @@
       </c>
       <c r="E63" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F63" s="12" t="inlineStr">
@@ -16593,7 +16593,7 @@
       </c>
       <c r="G63" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours inserts FST after LGT; check before cash is open. BDOI's review comment: “Confirm first with Insurers for payment hierarchy”.</t>
+          <t>Available: Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -16628,7 +16628,7 @@
       </c>
       <c r="G64" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -16663,7 +16663,7 @@
       </c>
       <c r="G65" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -16698,7 +16698,7 @@
       </c>
       <c r="G66" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -16733,7 +16733,7 @@
       </c>
       <c r="G67" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -16758,7 +16758,7 @@
       </c>
       <c r="E68" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F68" s="12" t="inlineStr">
@@ -16768,7 +16768,7 @@
       </c>
       <c r="G68" s="12" t="inlineStr">
         <is>
-          <t>The 98% application for 2% CWT clients is available; the tag per account follows decision C26.</t>
+          <t>Available: Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -16793,7 +16793,7 @@
       </c>
       <c r="E69" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
@@ -16803,7 +16803,7 @@
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
-          <t>One OR per group is issued; the print queue is planned for.</t>
+          <t>Available: Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -16838,7 +16838,7 @@
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -16873,7 +16873,7 @@
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -16898,7 +16898,7 @@
       </c>
       <c r="E72" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F72" s="12" t="inlineStr">
@@ -16908,7 +16908,7 @@
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
-          <t>Template maintenance of the AR and OR forms planned for (C16).</t>
+          <t>Available: Receipt form tests: AR and OR forms with the company address and VAT TIN, the amount in words and in figures, footer lines and copy label; a form change printed only after another user approved it. Certification of Payment test with its series number.</t>
         </is>
       </c>
     </row>
@@ -16933,7 +16933,7 @@
       </c>
       <c r="E73" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
@@ -16943,7 +16943,7 @@
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
-          <t>The OR PDF is available with the company name; BDOI's header, footer and words are planned for.</t>
+          <t>Available: Receipt form tests: AR and OR forms with the company address and VAT TIN, the amount in words and in figures, footer lines and copy label; a form change printed only after another user approved it. Certification of Payment test with its series number.</t>
         </is>
       </c>
     </row>
@@ -16968,7 +16968,7 @@
       </c>
       <c r="E74" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F74" s="12" t="inlineStr">
@@ -16978,7 +16978,7 @@
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
-          <t>The AR PDF is available; BDOI's form is planned for.</t>
+          <t>Available: Receipt form tests: AR and OR forms with the company address and VAT TIN, the amount in words and in figures, footer lines and copy label; a form change printed only after another user approved it. Certification of Payment test with its series number.</t>
         </is>
       </c>
     </row>
@@ -17013,7 +17013,7 @@
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -17038,7 +17038,7 @@
       </c>
       <c r="E76" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F76" s="12" t="inlineStr">
@@ -17048,7 +17048,7 @@
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours cancels one receipt per request. Ours has the BRD list in four groups (premium, commission, PDC, general); no restriction by payment type.</t>
+          <t>Available: Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -17073,7 +17073,7 @@
       </c>
       <c r="E77" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
@@ -17083,7 +17083,7 @@
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
-          <t>Reason, waiting request and disposition checks are available; the check-payment restriction is planned for (C21).</t>
+          <t>Available: Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -17108,7 +17108,7 @@
       </c>
       <c r="E78" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F78" s="12" t="inlineStr">
@@ -17118,7 +17118,7 @@
       </c>
       <c r="G78" s="12" t="inlineStr">
         <is>
-          <t>Reason, waiting request and disposition checks are available; the check-payment restriction is planned for (C21).</t>
+          <t>Available: Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -17143,7 +17143,7 @@
       </c>
       <c r="E79" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
@@ -17153,7 +17153,7 @@
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
-          <t>Reason, waiting request and disposition checks are available; the check-payment restriction is planned for (C21).</t>
+          <t>Available: Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -17178,7 +17178,7 @@
       </c>
       <c r="E80" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F80" s="12" t="inlineStr">
@@ -17188,7 +17188,7 @@
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
-          <t>Reversal and four eyes are available; the remitted branch follows decision C9.</t>
+          <t>Available: Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -17213,7 +17213,7 @@
       </c>
       <c r="E81" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F81" s="12" t="inlineStr">
@@ -17223,7 +17223,7 @@
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
-          <t>Reversal and four eyes are available; the remitted branch follows decision C9.</t>
+          <t>Available: Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -17248,7 +17248,7 @@
       </c>
       <c r="E82" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F82" s="12" t="inlineStr">
@@ -17258,7 +17258,7 @@
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
-          <t>Reversal and four eyes are available; the remitted branch follows decision C9.</t>
+          <t>Available: Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -17283,7 +17283,7 @@
       </c>
       <c r="E83" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F83" s="12" t="inlineStr">
@@ -17293,7 +17293,7 @@
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
-          <t>Reversal and four eyes are available; the remitted branch follows decision C9.</t>
+          <t>Available: Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -17328,7 +17328,7 @@
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -17363,7 +17363,7 @@
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -17388,7 +17388,7 @@
       </c>
       <c r="E86" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F86" s="12" t="inlineStr">
@@ -17398,7 +17398,7 @@
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
-          <t>The CSHID.005 information is captured; reinstatement of an issued receipt by account follows decision C2.</t>
+          <t>Available: Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -17423,7 +17423,7 @@
       </c>
       <c r="E87" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F87" s="12" t="inlineStr">
@@ -17433,7 +17433,7 @@
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
-          <t>The CSHID.005 information is captured; reinstatement of an issued receipt by account follows decision C2.</t>
+          <t>Available: Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -17468,7 +17468,7 @@
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -17493,7 +17493,7 @@
       </c>
       <c r="E89" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F89" s="12" t="inlineStr">
@@ -17503,7 +17503,7 @@
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
-          <t>Reinstatement of an issued receipt follows decision C2.</t>
+          <t>Available: Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -17528,7 +17528,7 @@
       </c>
       <c r="E90" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F90" s="12" t="inlineStr">
@@ -17538,7 +17538,7 @@
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
-          <t>Reinstatement of an issued receipt follows decision C2.</t>
+          <t>Available: Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -17563,7 +17563,7 @@
       </c>
       <c r="E91" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F91" s="12" t="inlineStr">
@@ -17573,7 +17573,7 @@
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
-          <t>Reinstatement of an issued receipt follows decision C2.</t>
+          <t>Available: Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -17598,7 +17598,7 @@
       </c>
       <c r="E92" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F92" s="12" t="inlineStr">
@@ -17608,7 +17608,7 @@
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
-          <t>Reinstatement of an issued receipt follows decision C2.</t>
+          <t>Available: Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -17643,7 +17643,7 @@
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -17668,7 +17668,7 @@
       </c>
       <c r="E94" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F94" s="12" t="inlineStr">
@@ -17678,7 +17678,7 @@
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours uploads one file at a time on the tab of its type (Bills Payment, Trade, CLPC, Direct Credit, PDC).</t>
+          <t>Available: Payment file tests: Bills Payment, CLPC, Trade, Direct Credit, post-dated check and commission schedule files in the client's layouts; name convention, size limit, duplicate file and rows, header count and total, TOTAL row; run report per category; legacy numbers as match keys; Direct Credit identification; files received via MFT with the alert of a refused file; channel simulator end to end.</t>
         </is>
       </c>
     </row>
@@ -17703,7 +17703,7 @@
       </c>
       <c r="E95" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F95" s="12" t="inlineStr">
@@ -17713,7 +17713,7 @@
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
-          <t>MFT intake planned for with BDOI IT.</t>
+          <t>Available: Payment file tests: Bills Payment, CLPC, Trade, Direct Credit, post-dated check and commission schedule files in the client's layouts; name convention, size limit, duplicate file and rows, header count and total, TOTAL row; run report per category; legacy numbers as match keys; Direct Credit identification; files received via MFT with the alert of a refused file; channel simulator end to end.</t>
         </is>
       </c>
     </row>
@@ -17738,7 +17738,7 @@
       </c>
       <c r="E96" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F96" s="12" t="inlineStr">
@@ -17748,7 +17748,7 @@
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
-          <t>MFT intake planned for with BDOI IT.</t>
+          <t>Available: Payment file tests: Bills Payment, CLPC, Trade, Direct Credit, post-dated check and commission schedule files in the client's layouts; name convention, size limit, duplicate file and rows, header count and total, TOTAL row; run report per category; legacy numbers as match keys; Direct Credit identification; files received via MFT with the alert of a refused file; channel simulator end to end.</t>
         </is>
       </c>
     </row>
@@ -17773,7 +17773,7 @@
       </c>
       <c r="E97" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F97" s="12" t="inlineStr">
@@ -17783,7 +17783,7 @@
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
-          <t>Duplicate file refusal is available; file-name check and 50 MB planned for.</t>
+          <t>Available: Payment file tests: Bills Payment, CLPC, Trade, Direct Credit, post-dated check and commission schedule files in the client's layouts; name convention, size limit, duplicate file and rows, header count and total, TOTAL row; run report per category; legacy numbers as match keys; Direct Credit identification; files received via MFT with the alert of a refused file; channel simulator end to end.</t>
         </is>
       </c>
     </row>
@@ -17808,7 +17808,7 @@
       </c>
       <c r="E98" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F98" s="12" t="inlineStr">
@@ -17818,7 +17818,7 @@
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
-          <t>Duplicate file refusal is available; file-name check and 50 MB planned for.</t>
+          <t>Available: Payment file tests: Bills Payment, CLPC, Trade, Direct Credit, post-dated check and commission schedule files in the client's layouts; name convention, size limit, duplicate file and rows, header count and total, TOTAL row; run report per category; legacy numbers as match keys; Direct Credit identification; files received via MFT with the alert of a refused file; channel simulator end to end.</t>
         </is>
       </c>
     </row>
@@ -17843,7 +17843,7 @@
       </c>
       <c r="E99" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F99" s="12" t="inlineStr">
@@ -17853,7 +17853,7 @@
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
-          <t>Duplicate file refusal is available; file-name check and 50 MB planned for.</t>
+          <t>Available: Payment file tests: Bills Payment, CLPC, Trade, Direct Credit, post-dated check and commission schedule files in the client's layouts; name convention, size limit, duplicate file and rows, header count and total, TOTAL row; run report per category; legacy numbers as match keys; Direct Credit identification; files received via MFT with the alert of a refused file; channel simulator end to end.</t>
         </is>
       </c>
     </row>
@@ -17878,7 +17878,7 @@
       </c>
       <c r="E100" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F100" s="12" t="inlineStr">
@@ -17888,7 +17888,7 @@
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
-          <t>Configurable layouts are available; header totals and the TOTAL row planned for.</t>
+          <t>Available: Payment file tests: Bills Payment, CLPC, Trade, Direct Credit, post-dated check and commission schedule files in the client's layouts; name convention, size limit, duplicate file and rows, header count and total, TOTAL row; run report per category; legacy numbers as match keys; Direct Credit identification; files received via MFT with the alert of a refused file; channel simulator end to end.</t>
         </is>
       </c>
     </row>
@@ -17913,7 +17913,7 @@
       </c>
       <c r="E101" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F101" s="12" t="inlineStr">
@@ -17923,7 +17923,7 @@
       </c>
       <c r="G101" s="12" t="inlineStr">
         <is>
-          <t>Configurable layouts are available; header totals and the TOTAL row planned for.</t>
+          <t>Available: Payment file tests: Bills Payment, CLPC, Trade, Direct Credit, post-dated check and commission schedule files in the client's layouts; name convention, size limit, duplicate file and rows, header count and total, TOTAL row; run report per category; legacy numbers as match keys; Direct Credit identification; files received via MFT with the alert of a refused file; channel simulator end to end.</t>
         </is>
       </c>
     </row>
@@ -17948,7 +17948,7 @@
       </c>
       <c r="E102" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F102" s="12" t="inlineStr">
@@ -17958,7 +17958,7 @@
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
-          <t>Matching on account references and pre-booked is available; legacy numbers as keys planned for.</t>
+          <t>Available: Payment file tests: Bills Payment, CLPC, Trade, Direct Credit, post-dated check and commission schedule files in the client's layouts; name convention, size limit, duplicate file and rows, header count and total, TOTAL row; run report per category; legacy numbers as match keys; Direct Credit identification; files received via MFT with the alert of a refused file; channel simulator end to end.</t>
         </is>
       </c>
     </row>
@@ -17983,7 +17983,7 @@
       </c>
       <c r="E103" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F103" s="12" t="inlineStr">
@@ -17993,7 +17993,7 @@
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
-          <t>Matching on account references and pre-booked is available; legacy numbers as keys planned for.</t>
+          <t>Available: Payment file tests: Bills Payment, CLPC, Trade, Direct Credit, post-dated check and commission schedule files in the client's layouts; name convention, size limit, duplicate file and rows, header count and total, TOTAL row; run report per category; legacy numbers as match keys; Direct Credit identification; files received via MFT with the alert of a refused file; channel simulator end to end.</t>
         </is>
       </c>
     </row>
@@ -18018,7 +18018,7 @@
       </c>
       <c r="E104" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F104" s="12" t="inlineStr">
@@ -18028,7 +18028,7 @@
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
-          <t>An AR per uploaded payment is available; the For Printing status is planned for.</t>
+          <t>Available: Payment file tests: Bills Payment, CLPC, Trade, Direct Credit, post-dated check and commission schedule files in the client's layouts; name convention, size limit, duplicate file and rows, header count and total, TOTAL row; run report per category; legacy numbers as match keys; Direct Credit identification; files received via MFT with the alert of a refused file; channel simulator end to end.</t>
         </is>
       </c>
     </row>
@@ -18053,7 +18053,7 @@
       </c>
       <c r="E105" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F105" s="12" t="inlineStr">
@@ -18063,7 +18063,7 @@
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours reports counts per outcome and the rows with their messages; amounts per category and some columns are not listed.</t>
+          <t>Available: Payment file tests: Bills Payment, CLPC, Trade, Direct Credit, post-dated check and commission schedule files in the client's layouts; name convention, size limit, duplicate file and rows, header count and total, TOTAL row; run report per category; legacy numbers as match keys; Direct Credit identification; files received via MFT with the alert of a refused file; channel simulator end to end.</t>
         </is>
       </c>
     </row>
@@ -18088,7 +18088,7 @@
       </c>
       <c r="E106" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F106" s="12" t="inlineStr">
@@ -18098,7 +18098,7 @@
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours reports counts per outcome and the rows with their messages; amounts per category and some columns are not listed.</t>
+          <t>Available: Payment file tests: Bills Payment, CLPC, Trade, Direct Credit, post-dated check and commission schedule files in the client's layouts; name convention, size limit, duplicate file and rows, header count and total, TOTAL row; run report per category; legacy numbers as match keys; Direct Credit identification; files received via MFT with the alert of a refused file; channel simulator end to end.</t>
         </is>
       </c>
     </row>
@@ -18123,7 +18123,7 @@
       </c>
       <c r="E107" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F107" s="12" t="inlineStr">
@@ -18133,7 +18133,7 @@
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
-          <t>Cashiering works the list; Marketing and Commission Receivable access follows decision C13.</t>
+          <t>Available: Unapplied payment list test: filters by type, payment date, insurer, client, assured, account and part of the number in any case; source, account, PN and loan application numbers, client and insurer; a fully applied payment leaves the list; a Marketing user sees the payments of his or her unit only.</t>
         </is>
       </c>
     </row>
@@ -18158,7 +18158,7 @@
       </c>
       <c r="E108" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F108" s="12" t="inlineStr">
@@ -18168,7 +18168,7 @@
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours searches reference or payor and filters origin; columns reference, payor, client, unit, amount, balance, disposition, received, stage.</t>
+          <t>Available: Unapplied payment list test: filters by type, payment date, insurer, client, assured, account and part of the number in any case; source, account, PN and loan application numbers, client and insurer; a fully applied payment leaves the list; a Marketing user sees the payments of his or her unit only.</t>
         </is>
       </c>
     </row>
@@ -18193,7 +18193,7 @@
       </c>
       <c r="E109" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F109" s="12" t="inlineStr">
@@ -18203,7 +18203,7 @@
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
-          <t>The record holds its source, amounts and history; PN or loan application number and insurer columns planned for.</t>
+          <t>Available: Unapplied payment list test: filters by type, payment date, insurer, client, assured, account and part of the number in any case; source, account, PN and loan application numbers, client and insurer; a fully applied payment leaves the list; a Marketing user sees the payments of his or her unit only.</t>
         </is>
       </c>
     </row>
@@ -18228,7 +18228,7 @@
       </c>
       <c r="E110" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F110" s="12" t="inlineStr">
@@ -18238,7 +18238,7 @@
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours adds DST payment application and Others, with an approval rule per type; reclass and transfer move the whole balance.</t>
+          <t>Available: Unapplied disposition tests: apply to another invoice through the hierarchy, refund through Disbursement with Team approval, reclass and transfer of the remaining balance, tabs per status and bulk submission and approval.</t>
         </is>
       </c>
     </row>
@@ -18263,7 +18263,7 @@
       </c>
       <c r="E111" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F111" s="12" t="inlineStr">
@@ -18273,7 +18273,7 @@
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours adds DST payment application and Others, with an approval rule per type; reclass and transfer move the whole balance.</t>
+          <t>Available: Unapplied disposition tests: apply to another invoice through the hierarchy, refund through Disbursement with Team approval, reclass and transfer of the remaining balance, tabs per status and bulk submission and approval.</t>
         </is>
       </c>
     </row>
@@ -18298,7 +18298,7 @@
       </c>
       <c r="E112" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F112" s="12" t="inlineStr">
@@ -18308,7 +18308,7 @@
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours adds DST payment application and Others, with an approval rule per type; reclass and transfer move the whole balance.</t>
+          <t>Available: Unapplied disposition tests: apply to another invoice through the hierarchy, refund through Disbursement with Team approval, reclass and transfer of the remaining balance, tabs per status and bulk submission and approval.</t>
         </is>
       </c>
     </row>
@@ -18333,7 +18333,7 @@
       </c>
       <c r="E113" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F113" s="12" t="inlineStr">
@@ -18343,7 +18343,7 @@
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours adds DST payment application and Others, with an approval rule per type; reclass and transfer move the whole balance.</t>
+          <t>Available: Unapplied disposition tests: apply to another invoice through the hierarchy, refund through Disbursement with Team approval, reclass and transfer of the remaining balance, tabs per status and bulk submission and approval.</t>
         </is>
       </c>
     </row>
@@ -18378,7 +18378,7 @@
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: Unapplied disposition tests: apply to another invoice through the hierarchy, refund through Disbursement with Team approval, reclass and transfer of the remaining balance, tabs per status and bulk submission and approval.</t>
         </is>
       </c>
     </row>
@@ -18413,7 +18413,7 @@
       </c>
       <c r="G115" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: Unapplied disposition tests: apply to another invoice through the hierarchy, refund through Disbursement with Team approval, reclass and transfer of the remaining balance, tabs per status and bulk submission and approval.</t>
         </is>
       </c>
     </row>
@@ -18438,7 +18438,7 @@
       </c>
       <c r="E116" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F116" s="12" t="inlineStr">
@@ -18448,7 +18448,7 @@
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
-          <t>OR at the Disbursement approval follows decision C12; today the OR is issued at the remittance approval.</t>
+          <t>Available: Settlement OR tests: the commission OR of an insurer settlement waits for the approval of Disbursement and is then issued, one OR per insurer and batch with one line per invoice and the OR number on the batch; a cancelled payment request cancels it; issued at the remittance approval with the other setting.</t>
         </is>
       </c>
     </row>
@@ -18473,7 +18473,7 @@
       </c>
       <c r="E117" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F117" s="12" t="inlineStr">
@@ -18483,7 +18483,7 @@
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
-          <t>The remittance OR has one line per invoice; the mapping at the Disbursement approval follows C12.</t>
+          <t>Available: Settlement OR tests: the commission OR of an insurer settlement waits for the approval of Disbursement and is then issued, one OR per insurer and batch with one line per invoice and the OR number on the batch; a cancelled payment request cancels it; issued at the remittance approval with the other setting.</t>
         </is>
       </c>
     </row>
@@ -18508,7 +18508,7 @@
       </c>
       <c r="E118" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F118" s="12" t="inlineStr">
@@ -18518,7 +18518,7 @@
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours: one receipt search on the ten BRD criteria and Invoice 360 with components, receipts, remittances, adjustments and history; ACSL manual adjustments are not named.</t>
+          <t>Available: Receipt search tests on the inquiry criteria, single and combined, names by part in any case, and the search log listing each search with the user and the criteria in words for the Auditor and the Team Leader. Walkthrough of the account record inquiry.</t>
         </is>
       </c>
     </row>
@@ -18543,7 +18543,7 @@
       </c>
       <c r="E119" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F119" s="12" t="inlineStr">
@@ -18553,7 +18553,7 @@
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours: one receipt search on the ten BRD criteria and Invoice 360 with components, receipts, remittances, adjustments and history; ACSL manual adjustments are not named.</t>
+          <t>Available: Receipt search tests on the inquiry criteria, single and combined, names by part in any case, and the search log listing each search with the user and the criteria in words for the Auditor and the Team Leader. Walkthrough of the account record inquiry.</t>
         </is>
       </c>
     </row>
@@ -18578,7 +18578,7 @@
       </c>
       <c r="E120" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F120" s="12" t="inlineStr">
@@ -18588,7 +18588,7 @@
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours: one receipt search on the ten BRD criteria and Invoice 360 with components, receipts, remittances, adjustments and history; ACSL manual adjustments are not named.</t>
+          <t>Available: Receipt search tests on the inquiry criteria, single and combined, names by part in any case, and the search log listing each search with the user and the criteria in words for the Auditor and the Team Leader. Walkthrough of the account record inquiry.</t>
         </is>
       </c>
     </row>
@@ -18623,7 +18623,7 @@
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: Report tests: every Cashiering report runs and exports in every format, view and export rights apart, each run archived, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;.</t>
         </is>
       </c>
     </row>
@@ -18648,7 +18648,7 @@
       </c>
       <c r="E122" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F122" s="12" t="inlineStr">
@@ -18658,7 +18658,7 @@
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
-          <t>View and export rights and the archive are available; BDOI's file names are planned for.</t>
+          <t>Available: Report tests: every Cashiering report runs and exports in every format, view and export rights apart, each run archived, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;.</t>
         </is>
       </c>
     </row>
@@ -18683,7 +18683,7 @@
       </c>
       <c r="E123" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F123" s="12" t="inlineStr">
@@ -18693,7 +18693,7 @@
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
-          <t>View and export rights and the archive are available; BDOI's file names are planned for.</t>
+          <t>Available: Report tests: every Cashiering report runs and exports in every format, view and export rights apart, each run archived, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;.</t>
         </is>
       </c>
     </row>
@@ -18718,7 +18718,7 @@
       </c>
       <c r="E124" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F124" s="12" t="inlineStr">
@@ -18728,7 +18728,7 @@
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
-          <t>View and export rights and the archive are available; BDOI's file names are planned for.</t>
+          <t>Available: Report tests: every Cashiering report runs and exports in every format, view and export rights apart, each run archived, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;.</t>
         </is>
       </c>
     </row>
@@ -18753,7 +18753,7 @@
       </c>
       <c r="E125" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F125" s="12" t="inlineStr">
@@ -18763,7 +18763,7 @@
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
-          <t>Report layouts of BDOI's list are being aligned; 12 layouts are draft.</t>
+          <t>Available: Report tests: columns in the client's order with totals, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;, ageing brackets 0-30 to above 365, payment reversals with record, reason, creator and poster, summary per disposition, certification of payment with its series number.</t>
         </is>
       </c>
     </row>
@@ -18903,7 +18903,7 @@
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: Cashiering dashboard test: count and amount per receipt type and status for issuance, cancellation, reinstatement, returned records, unapplied payments and payment files; each item opens its list; shown within 5 seconds.</t>
         </is>
       </c>
     </row>
@@ -18938,7 +18938,7 @@
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: Cashiering dashboard test: count and amount per receipt type and status for issuance, cancellation, reinstatement, returned records, unapplied payments and payment files; each item opens its list; shown within 5 seconds.</t>
         </is>
       </c>
     </row>
@@ -18973,7 +18973,7 @@
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -19008,7 +19008,7 @@
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -19033,7 +19033,7 @@
       </c>
       <c r="E133" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F133" s="12" t="inlineStr">
@@ -19043,7 +19043,7 @@
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
-          <t>The receipts of the day are listed with their status; the totals per bank account are planned for.</t>
+          <t>Available: Receipt record tests: AR and OR creation records with entry type, bank account, receipting branch and remarks; the validation messages (currency, check date, amounts); submit for posting, return with a reason, edit and posting by another user with the AR or OR number issued. Day-end list test: totals per payment type and bank account.</t>
         </is>
       </c>
     </row>
@@ -19078,7 +19078,7 @@
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -19113,7 +19113,7 @@
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: OR creation record tests (OR types, payee, amounts and taxes, save, validation, submit, return, edit, cancel, audit trail) and payment file test of the commission schedule (pipe-delimited template, size limit, validation report, failed and successful lists, raw file kept read-only, line or whole-file processing by setting).</t>
         </is>
       </c>
     </row>
@@ -19148,7 +19148,7 @@
       </c>
       <c r="G136" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: Receipt series tests: series per receipting branch with its year and number format (prefix, year, branch indicator, sequence), authorised by another user, warning alert of the numbers left, OR series for Head Office only, end below the last number refused.</t>
         </is>
       </c>
     </row>
@@ -19173,7 +19173,7 @@
       </c>
       <c r="E137" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F137" s="12" t="inlineStr">
@@ -19183,7 +19183,7 @@
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
-          <t>Copy label planned for with BDOI's forms (C16).</t>
+          <t>Available: Receipt printing tests: print by branch or insurer and issue dates, print queue of the receipts the system generated, re-print by part of the number with the REPRINT mark and the print count, certificate number at the first print, Client's and company copies with the company copy kept on the receipt, ZIP of one PDF per receipt, at most 500 per batch, retry and skip in the print log. Walkthrough of the print preview.</t>
         </is>
       </c>
     </row>
@@ -19218,7 +19218,7 @@
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: Posting tests: posting list with filters, all or selected records, confirmation message, return with a reason, AR numbers by receipting branch and OR numbers of Head Office in sequence, check payments posted before cash, application hierarchy, BIR 2307 accounts applied less the PR 2307, one OR per commission schedule placed in the print queue, GL posting with the minimal balance reversal.</t>
         </is>
       </c>
     </row>
@@ -19243,7 +19243,7 @@
       </c>
       <c r="E139" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F139" s="12" t="inlineStr">
@@ -19253,7 +19253,7 @@
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
-          <t>The Certification of Payment PDF is available; its series number is planned for.</t>
+          <t>Available: Receipt form tests: AR and OR forms with the company address and VAT TIN, the amount in words and in figures, footer lines and copy label; a form change printed only after another user approved it. Certification of Payment test with its series number.</t>
         </is>
       </c>
     </row>
@@ -19288,7 +19288,7 @@
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: Cancellation record tests: AR numbers only or OR numbers only, reasons by payment type, validation messages, edit, save or cancel the record, submit for posting, return, posting with a remitted AR as an AR insurer refund and a cancelled OR as commission receivable.</t>
         </is>
       </c>
     </row>
@@ -19323,7 +19323,7 @@
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: Reinstatement record tests: search of issued receipts, full or partial reinstatement by account, reason and encoded fields, validation, submit, return and posting (remitted AR to AR insurer refund, AR not remitted to unapplied payment, OR to AP unapplied commission).</t>
         </is>
       </c>
     </row>
@@ -19358,7 +19358,7 @@
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: Payment file tests: Bills Payment, CLPC, Trade, Direct Credit, post-dated check and commission schedule files in the client's layouts; name convention, size limit, duplicate file and rows, header count and total, TOTAL row; run report per category; legacy numbers as match keys; Direct Credit identification; files received via MFT with the alert of a refused file; channel simulator end to end.</t>
         </is>
       </c>
     </row>
@@ -19393,7 +19393,7 @@
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: Unapplied payment list test: filters by type, payment date, insurer, client, assured, account and part of the number in any case; source, account, PN and loan application numbers, client and insurer; a fully applied payment leaves the list; a Marketing user sees the payments of his or her unit only.</t>
         </is>
       </c>
     </row>
@@ -19428,7 +19428,7 @@
       </c>
       <c r="G144" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: Settlement OR tests: the commission OR of an insurer settlement waits for the approval of Disbursement and is then issued, one OR per insurer and batch with one line per invoice and the OR number on the batch; a cancelled payment request cancels it; issued at the remittance approval with the other setting.</t>
         </is>
       </c>
     </row>
@@ -19453,7 +19453,7 @@
       </c>
       <c r="E145" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F145" s="12" t="inlineStr">
@@ -19463,7 +19463,7 @@
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the platform: Ours: one receipt search on the ten BRD criteria and Invoice 360 with components, receipts, remittances, adjustments and history; ACSL manual adjustments are not named.</t>
+          <t>Available: Receipt search tests on the inquiry criteria, single and combined, names by part in any case, and the search log listing each search with the user and the criteria in words for the Auditor and the Team Leader. Walkthrough of the account record inquiry.</t>
         </is>
       </c>
     </row>
@@ -19498,7 +19498,7 @@
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: Report tests: every Cashiering report runs and exports in every format, view and export rights apart, each run archived, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;.</t>
         </is>
       </c>
     </row>
@@ -19533,7 +19533,7 @@
       </c>
       <c r="G147" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: Report tests: columns in the client's order with totals, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;, ageing brackets 0-30 to above 365, payment reversals with record, reason, creator and poster, summary per disposition, certification of payment with its series number.</t>
         </is>
       </c>
     </row>
@@ -19568,7 +19568,7 @@
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: Report tests: columns in the client's order with totals, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;, ageing brackets 0-30 to above 365, payment reversals with record, reason, creator and poster, summary per disposition, certification of payment with its series number.</t>
         </is>
       </c>
     </row>
@@ -19593,7 +19593,7 @@
       </c>
       <c r="E149" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F149" s="12" t="inlineStr">
@@ -19603,7 +19603,7 @@
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
-          <t>Layout draft.</t>
+          <t>Available: Report tests: columns in the client's order with totals, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;, ageing brackets 0-30 to above 365, payment reversals with record, reason, creator and poster, summary per disposition, certification of payment with its series number.</t>
         </is>
       </c>
     </row>
@@ -19628,7 +19628,7 @@
       </c>
       <c r="E150" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F150" s="12" t="inlineStr">
@@ -19638,7 +19638,7 @@
       </c>
       <c r="G150" s="12" t="inlineStr">
         <is>
-          <t>Ageing brackets of BDOI planned for.</t>
+          <t>Available: Report tests: columns in the client's order with totals, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;, ageing brackets 0-30 to above 365, payment reversals with record, reason, creator and poster, summary per disposition, certification of payment with its series number.</t>
         </is>
       </c>
     </row>
@@ -19673,7 +19673,7 @@
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: Report tests: columns in the client's order with totals, files named &lt;Report Name&gt;_&lt;MMDDYYYY&gt;, ageing brackets 0-30 to above 365, payment reversals with record, reason, creator and poster, summary per disposition, certification of payment with its series number.</t>
         </is>
       </c>
     </row>
@@ -20338,7 +20338,7 @@
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
-          <t>Available; confirmed with the acceptance test case in UAT.</t>
+          <t>Available: Payment file test: a file received via MFT and refused raises the alert to the Cashiering Team Leader; receipt series and pre-booked alerts.</t>
         </is>
       </c>
     </row>
@@ -20363,7 +20363,7 @@
       </c>
       <c r="E171" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F171" s="12" t="inlineStr">
@@ -20373,7 +20373,7 @@
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
-          <t>Series and pre-booked alerts are available; the alert for a refused MFT file is planned for.</t>
+          <t>Available: Payment file test: a file received via MFT and refused raises the alert to the Cashiering Team Leader; receipt series and pre-booked alerts.</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/out/Programme/Quality/BIBS_Coverage_BRD-02_FRS_Coverage_in_BIBS_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/Quality/BIBS_Coverage_BRD-02_FRS_Coverage_in_BIBS_v1.0.xlsx
@@ -746,7 +746,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>9 October 2026</t>
+          <t>10 October 2026</t>
         </is>
       </c>
     </row>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>3 test cases; Conformance register: FR-OP-003 {'Partly conformant': 3}</t>
+          <t>4 test cases; Conformance register: FR-OP-003 {'Partly conformant': 3}</t>
         </is>
       </c>
       <c r="H9" s="12" t="inlineStr">
@@ -3118,7 +3118,7 @@
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>6 test cases; Conformance register: FR-OP-003 {'Partly conformant': 3}</t>
+          <t>7 test cases; Conformance register: FR-OP-003 {'Partly conformant': 3}</t>
         </is>
       </c>
       <c r="H10" s="12" t="inlineStr">
@@ -3202,7 +3202,7 @@
       </c>
       <c r="G12" s="12" t="inlineStr">
         <is>
-          <t>11 test cases; Conformance register: FR-OP-003 {'Partly conformant': 3}; FR-OP-022 {'Conformant': 4} | Walkthrough WT-B.8, WT-B.9, WT-E.5, WT-E.6</t>
+          <t>13 test cases; Conformance register: FR-OP-003 {'Partly conformant': 3}; FR-OP-022 {'Conformant': 4} | Walkthrough WT-B.8, WT-B.9, WT-E.5, WT-E.6</t>
         </is>
       </c>
       <c r="H12" s="12" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>9 test cases; Conformance register: FR-OP-011 {'Conformant': 3}; FR-OP-002 {'Partly conformant': 3} | Walkthrough WT-A.3, WT-A.4, WT-D.3, WT-D.4, WT-E.8</t>
+          <t>13 test cases; Conformance register: FR-OP-011 {'Conformant': 3}; FR-OP-002 {'Partly conformant': 3} | Walkthrough WT-A.3, WT-A.4, WT-D.3, WT-D.4, WT-E.8</t>
         </is>
       </c>
       <c r="H13" s="12" t="inlineStr">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>14 test cases; Conformance register: FR-OP-011 {'Conformant': 3}; FR-OP-018 {'Conformant': 4} | Walkthrough WT-A.3, WT-A.4, WT-D.3, WT-D.4, WT-E.3, WT-E.8</t>
+          <t>18 test cases; Conformance register: FR-OP-011 {'Conformant': 3}; FR-OP-018 {'Conformant': 4} | Walkthrough WT-A.3, WT-A.4, WT-D.3, WT-D.4, WT-E.3, WT-E.8</t>
         </is>
       </c>
       <c r="H14" s="12" t="inlineStr">
@@ -3328,7 +3328,7 @@
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>15 test cases; Conformance register: FR-OP-018 {'Conformant': 4}; FR-OP-019 {'Conformant': 2}; FR-OP-011 {'Conformant': 3} | Walkthrough WT-A.3, WT-A.4, WT-D.3, WT-D.4, WT-E.3, WT-E.8</t>
+          <t>19 test cases; Conformance register: FR-OP-018 {'Conformant': 4}; FR-OP-019 {'Conformant': 2}; FR-OP-011 {'Conformant': 3} | Walkthrough WT-A.3, WT-A.4, WT-D.3, WT-D.4, WT-E.3, WT-E.8</t>
         </is>
       </c>
       <c r="H15" s="12" t="inlineStr">
@@ -3370,7 +3370,7 @@
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>5 test cases; Conformance register: FR-OP-011 {'Conformant': 3} | Walkthrough WT-A.3, WT-A.4, WT-D.3, WT-D.4, WT-E.8</t>
+          <t>9 test cases; Conformance register: FR-OP-011 {'Conformant': 3} | Walkthrough WT-A.3, WT-A.4, WT-D.3, WT-D.4, WT-E.8</t>
         </is>
       </c>
       <c r="H16" s="12" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>5 test cases; Conformance register: FR-OP-011 {'Conformant': 3} | Walkthrough WT-A.3, WT-A.4, WT-D.3, WT-D.4, WT-E.8</t>
+          <t>9 test cases; Conformance register: FR-OP-011 {'Conformant': 3} | Walkthrough WT-A.3, WT-A.4, WT-D.3, WT-D.4, WT-E.8</t>
         </is>
       </c>
       <c r="H17" s="12" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>30 test cases</t>
+          <t>36 test cases</t>
         </is>
       </c>
       <c r="H18" s="12" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>30 test cases</t>
+          <t>36 test cases</t>
         </is>
       </c>
       <c r="H19" s="12" t="inlineStr">
@@ -3538,7 +3538,7 @@
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>9 test cases; Conformance register: FR-OP-011 {'Conformant': 3}; FR-OP-031 {'Conformant': 5} | Walkthrough WT-A.3, WT-A.4, WT-D.3, WT-D.4, WT-E.8</t>
+          <t>13 test cases; Conformance register: FR-OP-011 {'Conformant': 3}; FR-OP-031 {'Conformant': 5} | Walkthrough WT-A.3, WT-A.4, WT-D.3, WT-D.4, WT-E.8</t>
         </is>
       </c>
       <c r="H20" s="12" t="inlineStr">
@@ -3580,7 +3580,7 @@
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>5 test cases; Conformance register: FR-OP-011 {'Conformant': 3}; FR-OP-031 {'Conformant': 5} | Walkthrough WT-A.3, WT-A.4, WT-D.3, WT-D.4, WT-E.8</t>
+          <t>9 test cases; Conformance register: FR-OP-011 {'Conformant': 3}; FR-OP-031 {'Conformant': 5} | Walkthrough WT-A.3, WT-A.4, WT-D.3, WT-D.4, WT-E.8</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -3622,7 +3622,7 @@
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>5 test cases; Conformance register: FR-OP-011 {'Conformant': 3}; FR-OP-031 {'Conformant': 5} | Walkthrough WT-A.3, WT-A.4, WT-D.3, WT-D.4, WT-E.8</t>
+          <t>9 test cases; Conformance register: FR-OP-011 {'Conformant': 3}; FR-OP-031 {'Conformant': 5} | Walkthrough WT-A.3, WT-A.4, WT-D.3, WT-D.4, WT-E.8</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
@@ -3664,7 +3664,7 @@
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>5 test cases; Conformance register: FR-OP-011 {'Conformant': 3}; FR-OP-031 {'Conformant': 5} | Walkthrough WT-A.3, WT-A.4, WT-D.3, WT-D.4, WT-E.8</t>
+          <t>9 test cases; Conformance register: FR-OP-011 {'Conformant': 3}; FR-OP-031 {'Conformant': 5} | Walkthrough WT-A.3, WT-A.4, WT-D.3, WT-D.4, WT-E.8</t>
         </is>
       </c>
       <c r="H23" s="12" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>10 test cases; Conformance register: FR-OP-011 {'Conformant': 3}; FR-OP-002 {'Partly conformant': 3} | Walkthrough WT-A.3, WT-A.4, WT-D.3, WT-D.4, WT-E.8</t>
+          <t>14 test cases; Conformance register: FR-OP-011 {'Conformant': 3}; FR-OP-002 {'Partly conformant': 3} | Walkthrough WT-A.3, WT-A.4, WT-D.3, WT-D.4, WT-E.8</t>
         </is>
       </c>
       <c r="H25" s="12" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>30 test cases</t>
+          <t>36 test cases</t>
         </is>
       </c>
       <c r="H26" s="12" t="inlineStr">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>30 test cases</t>
+          <t>36 test cases</t>
         </is>
       </c>
       <c r="H27" s="12" t="inlineStr">
@@ -3874,7 +3874,7 @@
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>30 test cases</t>
+          <t>36 test cases</t>
         </is>
       </c>
       <c r="H28" s="12" t="inlineStr">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>30 test cases</t>
+          <t>36 test cases</t>
         </is>
       </c>
       <c r="H29" s="12" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>30 test cases</t>
+          <t>36 test cases</t>
         </is>
       </c>
       <c r="H30" s="12" t="inlineStr">
@@ -4000,7 +4000,7 @@
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>30 test cases</t>
+          <t>36 test cases</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -4042,7 +4042,7 @@
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>7 test cases; Conformance register: FR-OP-024 {'Conformant': 3} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.7</t>
+          <t>8 test cases; Conformance register: FR-OP-024 {'Conformant': 3} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.7</t>
         </is>
       </c>
       <c r="H32" s="12" t="inlineStr">
@@ -4168,7 +4168,7 @@
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>4 test cases; Conformance register: FR-OP-021 {'Conformant': 2}</t>
+          <t>5 test cases; Conformance register: FR-OP-021 {'Conformant': 2}</t>
         </is>
       </c>
       <c r="H35" s="12" t="inlineStr">
@@ -4210,7 +4210,7 @@
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
-          <t>4 test cases; Conformance register: FR-OP-021 {'Conformant': 2}</t>
+          <t>5 test cases; Conformance register: FR-OP-021 {'Conformant': 2}</t>
         </is>
       </c>
       <c r="H36" s="12" t="inlineStr">
@@ -4252,7 +4252,7 @@
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>11 test cases; Conformance register: FR-OP-021 {'Conformant': 2}; FR-OP-008 {'Conformant': 3} | Walkthrough WT-E.2</t>
+          <t>12 test cases; Conformance register: FR-OP-021 {'Conformant': 2}; FR-OP-008 {'Conformant': 3} | Walkthrough WT-E.2</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -4294,7 +4294,7 @@
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
-          <t>4 test cases; Conformance register: FR-OP-021 {'Conformant': 2}</t>
+          <t>5 test cases; Conformance register: FR-OP-021 {'Conformant': 2}</t>
         </is>
       </c>
       <c r="H38" s="12" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>4 test cases; Conformance register: FR-OP-021 {'Conformant': 2}</t>
+          <t>5 test cases; Conformance register: FR-OP-021 {'Conformant': 2}</t>
         </is>
       </c>
       <c r="H39" s="12" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
-          <t>4 test cases; Conformance register: FR-OP-021 {'Conformant': 2}</t>
+          <t>5 test cases; Conformance register: FR-OP-021 {'Conformant': 2}</t>
         </is>
       </c>
       <c r="H40" s="12" t="inlineStr">
@@ -4420,7 +4420,7 @@
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>4 test cases; Conformance register: FR-OP-021 {'Conformant': 2}</t>
+          <t>5 test cases; Conformance register: FR-OP-021 {'Conformant': 2}</t>
         </is>
       </c>
       <c r="H41" s="12" t="inlineStr">
@@ -4462,7 +4462,7 @@
       </c>
       <c r="G42" s="12" t="inlineStr">
         <is>
-          <t>4 test cases; Conformance register: FR-OP-021 {'Conformant': 2}</t>
+          <t>5 test cases; Conformance register: FR-OP-021 {'Conformant': 2}</t>
         </is>
       </c>
       <c r="H42" s="12" t="inlineStr">
@@ -4504,7 +4504,7 @@
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>4 test cases; Conformance register: FR-OP-021 {'Conformant': 2}</t>
+          <t>5 test cases; Conformance register: FR-OP-021 {'Conformant': 2}</t>
         </is>
       </c>
       <c r="H43" s="12" t="inlineStr">
@@ -4546,7 +4546,7 @@
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
-          <t>5 test cases; Conformance register: FR-OP-021 {'Conformant': 2}</t>
+          <t>6 test cases; Conformance register: FR-OP-021 {'Conformant': 2}</t>
         </is>
       </c>
       <c r="H44" s="12" t="inlineStr">
@@ -4630,7 +4630,7 @@
       </c>
       <c r="G46" s="12" t="inlineStr">
         <is>
-          <t>6 test cases; Conformance register: FR-OP-021 {'Conformant': 2}</t>
+          <t>7 test cases; Conformance register: FR-OP-021 {'Conformant': 2}</t>
         </is>
       </c>
       <c r="H46" s="12" t="inlineStr">
@@ -4672,7 +4672,7 @@
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
-          <t>4 test cases; Conformance register: FR-OP-021 {'Conformant': 2}</t>
+          <t>5 test cases; Conformance register: FR-OP-021 {'Conformant': 2}</t>
         </is>
       </c>
       <c r="H47" s="12" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
-          <t>4 test cases; Conformance register: FR-OP-021 {'Conformant': 2}</t>
+          <t>5 test cases; Conformance register: FR-OP-021 {'Conformant': 2}</t>
         </is>
       </c>
       <c r="H48" s="12" t="inlineStr">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
-          <t>4 test cases; Conformance register: FR-OP-021 {'Conformant': 2}</t>
+          <t>5 test cases; Conformance register: FR-OP-021 {'Conformant': 2}</t>
         </is>
       </c>
       <c r="H49" s="12" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
-          <t>4 test cases; Conformance register: FR-OP-021 {'Conformant': 2}</t>
+          <t>5 test cases; Conformance register: FR-OP-021 {'Conformant': 2}</t>
         </is>
       </c>
       <c r="H50" s="12" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
-          <t>4 test cases; Conformance register: FR-OP-021 {'Conformant': 2}</t>
+          <t>5 test cases; Conformance register: FR-OP-021 {'Conformant': 2}</t>
         </is>
       </c>
       <c r="H51" s="12" t="inlineStr">
@@ -5764,7 +5764,7 @@
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
-          <t>3 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
+          <t>5 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
         </is>
       </c>
       <c r="H73" s="12" t="inlineStr">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
-          <t>8 test cases; Conformance register: FR-OP-025 {'Conformant': 2}; FR-OP-015 {'Conformant': 3} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.2, WT-E.9</t>
+          <t>12 test cases; Conformance register: FR-OP-025 {'Conformant': 2}; FR-OP-015 {'Conformant': 3} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.2, WT-E.9</t>
         </is>
       </c>
       <c r="H74" s="12" t="inlineStr">
@@ -5848,7 +5848,7 @@
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
-          <t>3 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
+          <t>5 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
         </is>
       </c>
       <c r="H75" s="12" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
-          <t>3 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
+          <t>5 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
         </is>
       </c>
       <c r="H76" s="12" t="inlineStr">
@@ -5932,7 +5932,7 @@
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
-          <t>4 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
+          <t>6 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
         </is>
       </c>
       <c r="H77" s="12" t="inlineStr">
@@ -5974,7 +5974,7 @@
       </c>
       <c r="G78" s="12" t="inlineStr">
         <is>
-          <t>3 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
+          <t>5 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
         </is>
       </c>
       <c r="H78" s="12" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
-          <t>4 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
+          <t>6 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
         </is>
       </c>
       <c r="H79" s="12" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
-          <t>3 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
+          <t>5 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
         </is>
       </c>
       <c r="H80" s="12" t="inlineStr">
@@ -6100,7 +6100,7 @@
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
-          <t>3 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
+          <t>5 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
         </is>
       </c>
       <c r="H81" s="12" t="inlineStr">
@@ -6142,7 +6142,7 @@
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
-          <t>3 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
+          <t>5 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
         </is>
       </c>
       <c r="H82" s="12" t="inlineStr">
@@ -6184,7 +6184,7 @@
       </c>
       <c r="G83" s="12" t="inlineStr">
         <is>
-          <t>3 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
+          <t>5 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
         </is>
       </c>
       <c r="H83" s="12" t="inlineStr">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="G84" s="12" t="inlineStr">
         <is>
-          <t>3 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
+          <t>5 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
         </is>
       </c>
       <c r="H84" s="12" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="G85" s="12" t="inlineStr">
         <is>
-          <t>3 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
+          <t>5 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
         </is>
       </c>
       <c r="H85" s="12" t="inlineStr">
@@ -6310,7 +6310,7 @@
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
-          <t>3 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
+          <t>5 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
         </is>
       </c>
       <c r="H86" s="12" t="inlineStr">
@@ -6352,7 +6352,7 @@
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
-          <t>3 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
+          <t>5 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
         </is>
       </c>
       <c r="H87" s="12" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
-          <t>4 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
+          <t>6 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
         </is>
       </c>
       <c r="H88" s="12" t="inlineStr">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
-          <t>3 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
+          <t>5 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
         </is>
       </c>
       <c r="H89" s="12" t="inlineStr">
@@ -6478,7 +6478,7 @@
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
-          <t>3 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
+          <t>5 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
         </is>
       </c>
       <c r="H90" s="12" t="inlineStr">
@@ -6520,7 +6520,7 @@
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
-          <t>3 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
+          <t>5 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
         </is>
       </c>
       <c r="H91" s="12" t="inlineStr">
@@ -6562,7 +6562,7 @@
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
-          <t>10 test cases; Conformance register: FR-OP-025 {'Conformant': 2}; FR-OP-024 {'Conformant': 3} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.7, WT-E.9</t>
+          <t>13 test cases; Conformance register: FR-OP-025 {'Conformant': 2}; FR-OP-024 {'Conformant': 3} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.7, WT-E.9</t>
         </is>
       </c>
       <c r="H92" s="12" t="inlineStr">
@@ -6604,7 +6604,7 @@
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
-          <t>54 test cases</t>
+          <t>62 test cases</t>
         </is>
       </c>
       <c r="H93" s="12" t="inlineStr">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
-          <t>54 test cases</t>
+          <t>62 test cases</t>
         </is>
       </c>
       <c r="H94" s="12" t="inlineStr">
@@ -6688,7 +6688,7 @@
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
-          <t>54 test cases</t>
+          <t>62 test cases</t>
         </is>
       </c>
       <c r="H95" s="12" t="inlineStr">
@@ -6730,7 +6730,7 @@
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
-          <t>54 test cases</t>
+          <t>62 test cases</t>
         </is>
       </c>
       <c r="H96" s="12" t="inlineStr">
@@ -6772,7 +6772,7 @@
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
-          <t>54 test cases</t>
+          <t>62 test cases</t>
         </is>
       </c>
       <c r="H97" s="12" t="inlineStr">
@@ -6814,7 +6814,7 @@
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
-          <t>54 test cases</t>
+          <t>62 test cases</t>
         </is>
       </c>
       <c r="H98" s="12" t="inlineStr">
@@ -6856,7 +6856,7 @@
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
-          <t>54 test cases</t>
+          <t>62 test cases</t>
         </is>
       </c>
       <c r="H99" s="12" t="inlineStr">
@@ -6898,7 +6898,7 @@
       </c>
       <c r="G100" s="12" t="inlineStr">
         <is>
-          <t>11 test cases; Conformance register: FR-OP-011 {'Conformant': 3}; FR-OP-002 {'Partly conformant': 3} | Walkthrough WT-A.3, WT-A.4, WT-D.3, WT-D.4, WT-E.8</t>
+          <t>15 test cases; Conformance register: FR-OP-011 {'Conformant': 3}; FR-OP-002 {'Partly conformant': 3} | Walkthrough WT-A.3, WT-A.4, WT-D.3, WT-D.4, WT-E.8</t>
         </is>
       </c>
       <c r="H100" s="12" t="inlineStr">
@@ -7360,7 +7360,7 @@
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
-          <t>16 test cases; Conformance register: FR-OP-018 {'Conformant': 4}; FR-OP-019 {'Conformant': 2}; FR-OP-022 {'Conformant': 4} | Walkthrough WT-A.3, WT-B.8, WT-B.9, WT-E.3, WT-E.5, WT-E.6, WT-E.8</t>
+          <t>17 test cases; Conformance register: FR-OP-018 {'Conformant': 4}; FR-OP-019 {'Conformant': 2}; FR-OP-022 {'Conformant': 4} | Walkthrough WT-A.3, WT-B.8, WT-B.9, WT-E.3, WT-E.5, WT-E.6, WT-E.8</t>
         </is>
       </c>
       <c r="H111" s="12" t="inlineStr">
@@ -7822,7 +7822,7 @@
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
-          <t>8 test cases; Conformance register: FR-OP-021 {'Conformant': 2}; FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
+          <t>11 test cases; Conformance register: FR-OP-021 {'Conformant': 2}; FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
         </is>
       </c>
       <c r="H122" s="12" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
-          <t>4 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
+          <t>6 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
         </is>
       </c>
       <c r="H125" s="12" t="inlineStr">
@@ -7990,7 +7990,7 @@
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
-          <t>7 test cases; Conformance register: FR-OP-012 {'Conformant': 2}; FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.7, WT-E.9</t>
+          <t>9 test cases; Conformance register: FR-OP-012 {'Conformant': 2}; FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.7, WT-E.9</t>
         </is>
       </c>
       <c r="H126" s="12" t="inlineStr">
@@ -8032,7 +8032,7 @@
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
-          <t>9 test cases; Conformance register: FR-OP-011 {'Conformant': 3}; FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.3, WT-A.4, WT-D.3, WT-D.4, WT-E.8, WT-E.9</t>
+          <t>15 test cases; Conformance register: FR-OP-011 {'Conformant': 3}; FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.3, WT-A.4, WT-D.3, WT-D.4, WT-E.8, WT-E.9</t>
         </is>
       </c>
       <c r="H127" s="12" t="inlineStr">
@@ -10720,7 +10720,7 @@
       </c>
       <c r="G191" s="12" t="inlineStr">
         <is>
-          <t>8 test cases; Conformance register: FR-OP-015 {'Conformant': 3}; FR-OP-002 {'Partly conformant': 3} | Walkthrough WT-E.2</t>
+          <t>10 test cases; Conformance register: FR-OP-015 {'Conformant': 3}; FR-OP-002 {'Partly conformant': 3} | Walkthrough WT-E.2</t>
         </is>
       </c>
       <c r="H191" s="12" t="inlineStr">
@@ -10762,7 +10762,7 @@
       </c>
       <c r="G192" s="12" t="inlineStr">
         <is>
-          <t>4 test cases; Conformance register: FR-OP-015 {'Conformant': 3} | Walkthrough WT-E.2</t>
+          <t>6 test cases; Conformance register: FR-OP-015 {'Conformant': 3} | Walkthrough WT-E.2</t>
         </is>
       </c>
       <c r="H192" s="12" t="inlineStr">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="G193" s="12" t="inlineStr">
         <is>
-          <t>4 test cases; Conformance register: FR-OP-015 {'Conformant': 3} | Walkthrough WT-E.2</t>
+          <t>6 test cases; Conformance register: FR-OP-015 {'Conformant': 3} | Walkthrough WT-E.2</t>
         </is>
       </c>
       <c r="H193" s="12" t="inlineStr">
@@ -10846,7 +10846,7 @@
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
-          <t>13 test cases; Conformance register: FR-OP-015 {'Conformant': 3}; FR-OP-016 {'Conformant': 3}; FR-OP-131 {'Partly conformant': 2} | Walkthrough WT-E.2, WT-E.4</t>
+          <t>15 test cases; Conformance register: FR-OP-015 {'Conformant': 3}; FR-OP-016 {'Conformant': 3}; FR-OP-131 {'Partly conformant': 2} | Walkthrough WT-E.2, WT-E.4</t>
         </is>
       </c>
       <c r="H194" s="12" t="inlineStr">
@@ -10888,7 +10888,7 @@
       </c>
       <c r="G195" s="12" t="inlineStr">
         <is>
-          <t>11 test cases; Conformance register: FR-OP-015 {'Conformant': 3}; FR-OP-008 {'Conformant': 3} | Walkthrough WT-E.2</t>
+          <t>13 test cases; Conformance register: FR-OP-015 {'Conformant': 3}; FR-OP-008 {'Conformant': 3} | Walkthrough WT-E.2</t>
         </is>
       </c>
       <c r="H195" s="12" t="inlineStr">
@@ -10930,7 +10930,7 @@
       </c>
       <c r="G196" s="12" t="inlineStr">
         <is>
-          <t>10 test cases; Conformance register: FR-OP-015 {'Conformant': 3}; FR-OP-008 {'Conformant': 3} | Walkthrough WT-E.2</t>
+          <t>12 test cases; Conformance register: FR-OP-015 {'Conformant': 3}; FR-OP-008 {'Conformant': 3} | Walkthrough WT-E.2</t>
         </is>
       </c>
       <c r="H196" s="12" t="inlineStr">
@@ -10972,7 +10972,7 @@
       </c>
       <c r="G197" s="12" t="inlineStr">
         <is>
-          <t>4 test cases; Conformance register: FR-OP-015 {'Conformant': 3} | Walkthrough WT-E.2</t>
+          <t>6 test cases; Conformance register: FR-OP-015 {'Conformant': 3} | Walkthrough WT-E.2</t>
         </is>
       </c>
       <c r="H197" s="12" t="inlineStr">
@@ -11056,7 +11056,7 @@
       </c>
       <c r="G199" s="12" t="inlineStr">
         <is>
-          <t>4 test cases; Conformance register: FR-OP-015 {'Conformant': 3} | Walkthrough WT-E.2</t>
+          <t>6 test cases; Conformance register: FR-OP-015 {'Conformant': 3} | Walkthrough WT-E.2</t>
         </is>
       </c>
       <c r="H199" s="12" t="inlineStr">
@@ -11098,7 +11098,7 @@
       </c>
       <c r="G200" s="12" t="inlineStr">
         <is>
-          <t>8 test cases; Conformance register: FR-OP-015 {'Conformant': 3}; FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.2, WT-E.9</t>
+          <t>12 test cases; Conformance register: FR-OP-015 {'Conformant': 3}; FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.2, WT-E.9</t>
         </is>
       </c>
       <c r="H200" s="12" t="inlineStr">
@@ -11224,7 +11224,7 @@
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
-          <t>10 test cases; Conformance register: FR-OP-022 {'Conformant': 4}; FR-OP-002 {'Partly conformant': 3} | Walkthrough WT-B.8, WT-B.9, WT-E.5, WT-E.6</t>
+          <t>11 test cases; Conformance register: FR-OP-022 {'Conformant': 4}; FR-OP-002 {'Partly conformant': 3} | Walkthrough WT-B.8, WT-B.9, WT-E.5, WT-E.6</t>
         </is>
       </c>
       <c r="H203" s="12" t="inlineStr">
@@ -11266,7 +11266,7 @@
       </c>
       <c r="G204" s="12" t="inlineStr">
         <is>
-          <t>6 test cases; Conformance register: FR-OP-022 {'Conformant': 4} | Walkthrough WT-B.8, WT-B.9, WT-E.5, WT-E.6</t>
+          <t>7 test cases; Conformance register: FR-OP-022 {'Conformant': 4} | Walkthrough WT-B.8, WT-B.9, WT-E.5, WT-E.6</t>
         </is>
       </c>
       <c r="H204" s="12" t="inlineStr">
@@ -11308,7 +11308,7 @@
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
-          <t>7 test cases; Conformance register: FR-OP-022 {'Conformant': 4} | Walkthrough WT-B.8, WT-B.9, WT-E.5, WT-E.6</t>
+          <t>8 test cases; Conformance register: FR-OP-022 {'Conformant': 4} | Walkthrough WT-B.8, WT-B.9, WT-E.5, WT-E.6</t>
         </is>
       </c>
       <c r="H205" s="12" t="inlineStr">
@@ -11350,7 +11350,7 @@
       </c>
       <c r="G206" s="12" t="inlineStr">
         <is>
-          <t>6 test cases; Conformance register: FR-OP-022 {'Conformant': 4} | Walkthrough WT-B.8, WT-B.9, WT-E.5, WT-E.6</t>
+          <t>7 test cases; Conformance register: FR-OP-022 {'Conformant': 4} | Walkthrough WT-B.8, WT-B.9, WT-E.5, WT-E.6</t>
         </is>
       </c>
       <c r="H206" s="12" t="inlineStr">
@@ -11392,7 +11392,7 @@
       </c>
       <c r="G207" s="12" t="inlineStr">
         <is>
-          <t>6 test cases; Conformance register: FR-OP-022 {'Conformant': 4} | Walkthrough WT-B.8, WT-B.9, WT-E.5, WT-E.6</t>
+          <t>7 test cases; Conformance register: FR-OP-022 {'Conformant': 4} | Walkthrough WT-B.8, WT-B.9, WT-E.5, WT-E.6</t>
         </is>
       </c>
       <c r="H207" s="12" t="inlineStr">
@@ -11434,7 +11434,7 @@
       </c>
       <c r="G208" s="12" t="inlineStr">
         <is>
-          <t>6 test cases; Conformance register: FR-OP-022 {'Conformant': 4} | Walkthrough WT-B.8, WT-B.9, WT-E.5, WT-E.6</t>
+          <t>7 test cases; Conformance register: FR-OP-022 {'Conformant': 4} | Walkthrough WT-B.8, WT-B.9, WT-E.5, WT-E.6</t>
         </is>
       </c>
       <c r="H208" s="12" t="inlineStr">
@@ -11476,7 +11476,7 @@
       </c>
       <c r="G209" s="12" t="inlineStr">
         <is>
-          <t>7 test cases; Conformance register: FR-OP-022 {'Conformant': 4} | Walkthrough WT-B.8, WT-B.9, WT-E.5, WT-E.6</t>
+          <t>8 test cases; Conformance register: FR-OP-022 {'Conformant': 4} | Walkthrough WT-B.8, WT-B.9, WT-E.5, WT-E.6</t>
         </is>
       </c>
       <c r="H209" s="12" t="inlineStr">
@@ -11518,7 +11518,7 @@
       </c>
       <c r="G210" s="12" t="inlineStr">
         <is>
-          <t>13 test cases; Conformance register: FR-OP-022 {'Conformant': 4}; FR-OP-120 {'Conformant': 2} | Walkthrough WT-B.8, WT-B.9, WT-B.10, WT-E.5, WT-E.6</t>
+          <t>14 test cases; Conformance register: FR-OP-022 {'Conformant': 4}; FR-OP-120 {'Conformant': 2} | Walkthrough WT-B.8, WT-B.9, WT-B.10, WT-E.5, WT-E.6</t>
         </is>
       </c>
       <c r="H210" s="12" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="G211" s="12" t="inlineStr">
         <is>
-          <t>8 test cases; Conformance register: FR-OP-022 {'Conformant': 4} | Walkthrough WT-B.8, WT-B.9, WT-E.5, WT-E.6</t>
+          <t>9 test cases; Conformance register: FR-OP-022 {'Conformant': 4} | Walkthrough WT-B.8, WT-B.9, WT-E.5, WT-E.6</t>
         </is>
       </c>
       <c r="H211" s="12" t="inlineStr">
@@ -11644,7 +11644,7 @@
       </c>
       <c r="G213" s="12" t="inlineStr">
         <is>
-          <t>5 test cases; Conformance register: FR-OP-021 {'Conformant': 2}; FR-OP-035 {'Conformant': 3} | Walkthrough WT-A.7</t>
+          <t>6 test cases; Conformance register: FR-OP-021 {'Conformant': 2}; FR-OP-035 {'Conformant': 3} | Walkthrough WT-A.7</t>
         </is>
       </c>
       <c r="H213" s="12" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="G214" s="12" t="inlineStr">
         <is>
-          <t>4 test cases; Conformance register: FR-OP-021 {'Conformant': 2}</t>
+          <t>5 test cases; Conformance register: FR-OP-021 {'Conformant': 2}</t>
         </is>
       </c>
       <c r="H214" s="12" t="inlineStr">
@@ -11728,7 +11728,7 @@
       </c>
       <c r="G215" s="12" t="inlineStr">
         <is>
-          <t>4 test cases; Conformance register: FR-OP-035 {'Conformant': 3} | Walkthrough WT-A.7</t>
+          <t>5 test cases; Conformance register: FR-OP-035 {'Conformant': 3} | Walkthrough WT-A.7</t>
         </is>
       </c>
       <c r="H215" s="12" t="inlineStr">
@@ -11770,7 +11770,7 @@
       </c>
       <c r="G216" s="12" t="inlineStr">
         <is>
-          <t>5 test cases; Conformance register: FR-OP-035 {'Conformant': 3}; FR-OP-021 {'Conformant': 2} | Walkthrough WT-A.7</t>
+          <t>6 test cases; Conformance register: FR-OP-035 {'Conformant': 3}; FR-OP-021 {'Conformant': 2} | Walkthrough WT-A.7</t>
         </is>
       </c>
       <c r="H216" s="12" t="inlineStr">
@@ -11812,7 +11812,7 @@
       </c>
       <c r="G217" s="12" t="inlineStr">
         <is>
-          <t>11 test cases; Conformance register: FR-OP-024 {'Conformant': 3}; FR-OP-005 {'Conformant': 3} | Walkthrough WT-A.2, WT-A.4, WT-D.3, WT-D.4, WT-E.7</t>
+          <t>12 test cases; Conformance register: FR-OP-024 {'Conformant': 3}; FR-OP-005 {'Conformant': 3} | Walkthrough WT-A.2, WT-A.4, WT-D.3, WT-D.4, WT-E.7</t>
         </is>
       </c>
       <c r="H217" s="12" t="inlineStr">
@@ -11854,7 +11854,7 @@
       </c>
       <c r="G218" s="12" t="inlineStr">
         <is>
-          <t>5 test cases; Conformance register: FR-OP-024 {'Conformant': 3} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.7</t>
+          <t>6 test cases; Conformance register: FR-OP-024 {'Conformant': 3} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.7</t>
         </is>
       </c>
       <c r="H218" s="12" t="inlineStr">
@@ -11896,7 +11896,7 @@
       </c>
       <c r="G219" s="12" t="inlineStr">
         <is>
-          <t>16 test cases; Conformance register: FR-OP-005 {'Conformant': 3}; FR-OP-004 {'Conformant': 5}; FR-OP-024 {'Conformant': 3} | Walkthrough WT-A.2, WT-A.4, WT-D.3, WT-D.4, WT-E.7</t>
+          <t>17 test cases; Conformance register: FR-OP-005 {'Conformant': 3}; FR-OP-004 {'Conformant': 5}; FR-OP-024 {'Conformant': 3} | Walkthrough WT-A.2, WT-A.4, WT-D.3, WT-D.4, WT-E.7</t>
         </is>
       </c>
       <c r="H219" s="12" t="inlineStr">
@@ -11938,7 +11938,7 @@
       </c>
       <c r="G220" s="12" t="inlineStr">
         <is>
-          <t>6 test cases; Conformance register: FR-OP-009 {'Conformant': 3}; FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10, WT-E.11</t>
+          <t>7 test cases; Conformance register: FR-OP-009 {'Conformant': 3}; FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10, WT-E.11</t>
         </is>
       </c>
       <c r="H220" s="12" t="inlineStr">
@@ -12106,7 +12106,7 @@
       </c>
       <c r="G224" s="12" t="inlineStr">
         <is>
-          <t>4 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
+          <t>5 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
         </is>
       </c>
       <c r="H224" s="12" t="inlineStr">
@@ -12148,7 +12148,7 @@
       </c>
       <c r="G225" s="12" t="inlineStr">
         <is>
-          <t>3 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
+          <t>4 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
         </is>
       </c>
       <c r="H225" s="12" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="G226" s="12" t="inlineStr">
         <is>
-          <t>3 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
+          <t>4 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
         </is>
       </c>
       <c r="H226" s="12" t="inlineStr">
@@ -12232,7 +12232,7 @@
       </c>
       <c r="G227" s="12" t="inlineStr">
         <is>
-          <t>3 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
+          <t>4 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
         </is>
       </c>
       <c r="H227" s="12" t="inlineStr">
@@ -12274,7 +12274,7 @@
       </c>
       <c r="G228" s="12" t="inlineStr">
         <is>
-          <t>3 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
+          <t>4 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
         </is>
       </c>
       <c r="H228" s="12" t="inlineStr">
@@ -12316,7 +12316,7 @@
       </c>
       <c r="G229" s="12" t="inlineStr">
         <is>
-          <t>3 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
+          <t>4 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
         </is>
       </c>
       <c r="H229" s="12" t="inlineStr">
@@ -12358,7 +12358,7 @@
       </c>
       <c r="G230" s="12" t="inlineStr">
         <is>
-          <t>3 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
+          <t>4 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
         </is>
       </c>
       <c r="H230" s="12" t="inlineStr">
@@ -12400,7 +12400,7 @@
       </c>
       <c r="G231" s="12" t="inlineStr">
         <is>
-          <t>3 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
+          <t>4 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
         </is>
       </c>
       <c r="H231" s="12" t="inlineStr">
@@ -12442,7 +12442,7 @@
       </c>
       <c r="G232" s="12" t="inlineStr">
         <is>
-          <t>3 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
+          <t>4 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
         </is>
       </c>
       <c r="H232" s="12" t="inlineStr">
@@ -12484,7 +12484,7 @@
       </c>
       <c r="G233" s="12" t="inlineStr">
         <is>
-          <t>3 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
+          <t>4 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
         </is>
       </c>
       <c r="H233" s="12" t="inlineStr">
@@ -12526,7 +12526,7 @@
       </c>
       <c r="G234" s="12" t="inlineStr">
         <is>
-          <t>3 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
+          <t>4 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
         </is>
       </c>
       <c r="H234" s="12" t="inlineStr">
@@ -12568,7 +12568,7 @@
       </c>
       <c r="G235" s="12" t="inlineStr">
         <is>
-          <t>3 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
+          <t>4 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
         </is>
       </c>
       <c r="H235" s="12" t="inlineStr">
@@ -12610,7 +12610,7 @@
       </c>
       <c r="G236" s="12" t="inlineStr">
         <is>
-          <t>3 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
+          <t>4 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
         </is>
       </c>
       <c r="H236" s="12" t="inlineStr">
@@ -12652,7 +12652,7 @@
       </c>
       <c r="G237" s="12" t="inlineStr">
         <is>
-          <t>3 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
+          <t>4 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
         </is>
       </c>
       <c r="H237" s="12" t="inlineStr">
@@ -12694,7 +12694,7 @@
       </c>
       <c r="G238" s="12" t="inlineStr">
         <is>
-          <t>3 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
+          <t>4 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
         </is>
       </c>
       <c r="H238" s="12" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="G239" s="12" t="inlineStr">
         <is>
-          <t>3 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
+          <t>4 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
         </is>
       </c>
       <c r="H239" s="12" t="inlineStr">
@@ -12778,7 +12778,7 @@
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
-          <t>3 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
+          <t>4 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
         </is>
       </c>
       <c r="H240" s="12" t="inlineStr">
@@ -12820,7 +12820,7 @@
       </c>
       <c r="G241" s="12" t="inlineStr">
         <is>
-          <t>3 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
+          <t>4 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
         </is>
       </c>
       <c r="H241" s="12" t="inlineStr">
@@ -12862,7 +12862,7 @@
       </c>
       <c r="G242" s="12" t="inlineStr">
         <is>
-          <t>11 test cases</t>
+          <t>12 test cases</t>
         </is>
       </c>
       <c r="H242" s="12" t="inlineStr">
@@ -12988,7 +12988,7 @@
       </c>
       <c r="G245" s="12" t="inlineStr">
         <is>
-          <t>5 test cases; Conformance register: FR-OP-003 {'Partly conformant': 3}</t>
+          <t>6 test cases; Conformance register: FR-OP-003 {'Partly conformant': 3}</t>
         </is>
       </c>
       <c r="H245" s="12" t="inlineStr">
@@ -13072,7 +13072,7 @@
       </c>
       <c r="G247" s="12" t="inlineStr">
         <is>
-          <t>9 test cases; Conformance register: FR-OP-011 {'Conformant': 3}; FR-OP-028 {'Conformant': 2} | Walkthrough WT-A.3, WT-A.4, WT-D.3, WT-D.4, WT-E.8, WT-E.10</t>
+          <t>14 test cases; Conformance register: FR-OP-011 {'Conformant': 3}; FR-OP-028 {'Conformant': 2} | Walkthrough WT-A.3, WT-A.4, WT-D.3, WT-D.4, WT-E.8, WT-E.10</t>
         </is>
       </c>
       <c r="H247" s="12" t="inlineStr">
@@ -13198,7 +13198,7 @@
       </c>
       <c r="G250" s="12" t="inlineStr">
         <is>
-          <t>4 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
+          <t>6 test cases; Conformance register: FR-OP-025 {'Conformant': 2} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.9</t>
         </is>
       </c>
       <c r="H250" s="12" t="inlineStr">
@@ -13282,7 +13282,7 @@
       </c>
       <c r="G252" s="12" t="inlineStr">
         <is>
-          <t>4 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
+          <t>5 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
         </is>
       </c>
       <c r="H252" s="12" t="inlineStr">
@@ -13492,7 +13492,7 @@
       </c>
       <c r="G257" s="12" t="inlineStr">
         <is>
-          <t>5 test cases; Conformance register: FR-OP-021 {'Conformant': 2}</t>
+          <t>6 test cases; Conformance register: FR-OP-021 {'Conformant': 2}</t>
         </is>
       </c>
       <c r="H257" s="12" t="inlineStr">
@@ -13534,7 +13534,7 @@
       </c>
       <c r="G258" s="12" t="inlineStr">
         <is>
-          <t>6 test cases; Conformance register: FR-OP-024 {'Conformant': 3} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.7</t>
+          <t>7 test cases; Conformance register: FR-OP-024 {'Conformant': 3} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.7</t>
         </is>
       </c>
       <c r="H258" s="12" t="inlineStr">
@@ -13618,7 +13618,7 @@
       </c>
       <c r="G260" s="12" t="inlineStr">
         <is>
-          <t>8 test cases; Conformance register: FR-OP-028 {'Conformant': 2}; FR-OP-016 {'Conformant': 3} | Walkthrough WT-E.2, WT-E.4, WT-E.10</t>
+          <t>9 test cases; Conformance register: FR-OP-028 {'Conformant': 2}; FR-OP-016 {'Conformant': 3} | Walkthrough WT-E.2, WT-E.4, WT-E.10</t>
         </is>
       </c>
       <c r="H260" s="12" t="inlineStr">
@@ -13660,7 +13660,7 @@
       </c>
       <c r="G261" s="12" t="inlineStr">
         <is>
-          <t>4 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
+          <t>5 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
         </is>
       </c>
       <c r="H261" s="12" t="inlineStr">
@@ -13702,7 +13702,7 @@
       </c>
       <c r="G262" s="12" t="inlineStr">
         <is>
-          <t>4 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
+          <t>5 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
         </is>
       </c>
       <c r="H262" s="12" t="inlineStr">
@@ -13744,7 +13744,7 @@
       </c>
       <c r="G263" s="12" t="inlineStr">
         <is>
-          <t>4 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
+          <t>5 test cases; Conformance register: FR-OP-028 {'Conformant': 2} | Walkthrough WT-E.10</t>
         </is>
       </c>
       <c r="H263" s="12" t="inlineStr">
@@ -14038,7 +14038,7 @@
       </c>
       <c r="G270" s="12" t="inlineStr">
         <is>
-          <t>10 test cases; Conformance register: FR-OP-022 {'Conformant': 4}; FR-OP-130 {'Conformant': 2} | Walkthrough WT-B.8, WT-B.9, WT-E.5, WT-E.6</t>
+          <t>11 test cases; Conformance register: FR-OP-022 {'Conformant': 4}; FR-OP-130 {'Conformant': 2} | Walkthrough WT-B.8, WT-B.9, WT-E.5, WT-E.6</t>
         </is>
       </c>
       <c r="H270" s="12" t="inlineStr">
@@ -14080,7 +14080,7 @@
       </c>
       <c r="G271" s="12" t="inlineStr">
         <is>
-          <t>10 test cases; Conformance register: FR-OP-022 {'Conformant': 4}; FR-OP-130 {'Conformant': 2} | Walkthrough WT-B.8, WT-B.9, WT-E.5, WT-E.6</t>
+          <t>11 test cases; Conformance register: FR-OP-022 {'Conformant': 4}; FR-OP-130 {'Conformant': 2} | Walkthrough WT-B.8, WT-B.9, WT-E.5, WT-E.6</t>
         </is>
       </c>
       <c r="H271" s="12" t="inlineStr">
@@ -14164,7 +14164,7 @@
       </c>
       <c r="G273" s="12" t="inlineStr">
         <is>
-          <t>6 test cases; Conformance register: FR-OP-024 {'Conformant': 3} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.7</t>
+          <t>7 test cases; Conformance register: FR-OP-024 {'Conformant': 3} | Walkthrough WT-A.4, WT-D.3, WT-D.4, WT-E.7</t>
         </is>
       </c>
       <c r="H273" s="12" t="inlineStr">
@@ -14248,7 +14248,7 @@
       </c>
       <c r="G275" s="12" t="inlineStr">
         <is>
-          <t>4 test cases; Conformance register: FR-OP-003 {'Partly conformant': 3}</t>
+          <t>5 test cases; Conformance register: FR-OP-003 {'Partly conformant': 3}</t>
         </is>
       </c>
       <c r="H275" s="12" t="inlineStr">
@@ -14374,7 +14374,7 @@
       </c>
       <c r="G278" s="12" t="inlineStr">
         <is>
-          <t>14 test cases; Conformance register: FR-OP-013 {'Conformant': 3}; FR-OP-022 {'Conformant': 4}; FR-OP-120 {'Conformant': 2} | Walkthrough WT-A.4, WT-B.8, WT-B.9, WT-B.10, WT-D.3, WT-D.4, WT-E.5, WT-E.6</t>
+          <t>15 test cases; Conformance register: FR-OP-013 {'Conformant': 3}; FR-OP-022 {'Conformant': 4}; FR-OP-120 {'Conformant': 2} | Walkthrough WT-A.4, WT-B.8, WT-B.9, WT-B.10, WT-D.3, WT-D.4, WT-E.5, WT-E.6</t>
         </is>
       </c>
       <c r="H278" s="12" t="inlineStr">

--- a/docs/deliverables/out/Programme/Quality/BIBS_Coverage_BRD-02_FRS_Coverage_in_BIBS_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/Quality/BIBS_Coverage_BRD-02_FRS_Coverage_in_BIBS_v1.0.xlsx
@@ -746,7 +746,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>10 October 2026</t>
+          <t>11 October 2026</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/out/Programme/Quality/BIBS_Coverage_BRD-02_FRS_Coverage_in_BIBS_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/Quality/BIBS_Coverage_BRD-02_FRS_Coverage_in_BIBS_v1.0.xlsx
@@ -691,7 +691,7 @@
     <row r="8">
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>BRD-02 Operations Cashiering - FRS in BDOI's template v3.2 (internal)</t>
+          <t>BRD-02 Operations Cashiering - FRS in BDOI's template v3.3 (internal)</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>Coverage of the FRS v3.2 in the BIBS environment, by item and by acceptance criterion</t>
+          <t>Coverage of the FRS v3.3 in the BIBS environment, by item and by acceptance criterion</t>
         </is>
       </c>
       <c r="D21" s="14" t="n">
@@ -834,7 +834,7 @@
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>Every FR item and sub-item of the FRS v3.2</t>
+          <t>Every FR item and sub-item of the FRS v3.3</t>
         </is>
       </c>
       <c r="D22" s="12" t="n">
@@ -849,7 +849,7 @@
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>Every acceptance criterion of the FRS v3.2</t>
+          <t>Every acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
       <c r="D23" s="14" t="n">
@@ -1433,7 +1433,7 @@
     <row r="2">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>Coverage of the FRS v3.2 in the BIBS environment, by item and by acceptance criterion</t>
+          <t>Coverage of the FRS v3.3 in the BIBS environment, by item and by acceptance criterion</t>
         </is>
       </c>
     </row>
@@ -2819,7 +2819,7 @@
     <row r="2">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>Every FR item and sub-item of the FRS v3.2</t>
+          <t>Every FR item and sub-item of the FRS v3.3</t>
         </is>
       </c>
     </row>
@@ -14482,7 +14482,7 @@
     <row r="2">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>Every acceptance criterion of the FRS v3.2</t>
+          <t>Every acceptance criterion of the FRS v3.3</t>
         </is>
       </c>
     </row>
